--- a/inventario.xlsx.xlsx
+++ b/inventario.xlsx.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2746fa196ce476c0/Desktop/kiosco el tio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="11_F0BF34C6AB674EABCA5660F4A3CFFCC672003DE8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{59D68AD0-5D9A-49C7-8931-2D77F5C7264B}"/>
+  <xr:revisionPtr revIDLastSave="201" documentId="11_F0BF34C6AB674EABCA5660F4A3CFFCC672003DE8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B99619DB-0BD3-43BA-80C6-B8C1B7B89A34}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Comestibles" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="448" uniqueCount="433">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="457" uniqueCount="443">
   <si>
     <t>CODIGO</t>
   </si>
@@ -276,9 +276,6 @@
     <t>KESITAS CAJA X 125G</t>
   </si>
   <si>
-    <t>PAN HAMBURGUESA DON JOSE</t>
-  </si>
-  <si>
     <t>MANA RELLENA</t>
   </si>
   <si>
@@ -1336,6 +1333,39 @@
   </si>
   <si>
     <t>CURITAS</t>
+  </si>
+  <si>
+    <t>TERRABUSI ANILLO 300G</t>
+  </si>
+  <si>
+    <t>BLOCK 38G</t>
+  </si>
+  <si>
+    <t>ALFAJOR LAS COLONIAS</t>
+  </si>
+  <si>
+    <t>LAVANDINA X5</t>
+  </si>
+  <si>
+    <t>DETERGENTE MAGISTRAL 215CC</t>
+  </si>
+  <si>
+    <t>DESODORANTE DOVE BOLILLA</t>
+  </si>
+  <si>
+    <t>PAN HAMBURGUESA DON JOSE GDE</t>
+  </si>
+  <si>
+    <t>PAN HAMBURGUESA DON YEYO CHICO</t>
+  </si>
+  <si>
+    <t>I</t>
+  </si>
+  <si>
+    <t>SIDIET 250CC</t>
+  </si>
+  <si>
+    <t>YERBA MAÑANITA 500G</t>
   </si>
 </sst>
 </file>
@@ -1381,12 +1411,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1402,6 +1433,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1606,7 +1641,7 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.6640625" customWidth="1"/>
-    <col min="2" max="2" width="29.44140625" customWidth="1"/>
+    <col min="2" max="2" width="33.5546875" customWidth="1"/>
     <col min="3" max="3" width="15.6640625" customWidth="1"/>
     <col min="4" max="4" width="21.6640625" customWidth="1"/>
     <col min="5" max="26" width="10.6640625" customWidth="1"/>
@@ -1623,7 +1658,7 @@
         <v>6</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>3</v>
+        <v>440</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -1762,11 +1797,11 @@
         <v>35</v>
       </c>
       <c r="C10" s="1">
-        <v>1300</v>
+        <v>1050</v>
       </c>
       <c r="D10" s="1">
         <f t="shared" si="0"/>
-        <v>1900</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -1778,11 +1813,11 @@
         <v>39</v>
       </c>
       <c r="C11" s="1">
-        <v>1900</v>
+        <v>1400</v>
       </c>
       <c r="D11" s="1">
         <f t="shared" si="0"/>
-        <v>2700</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -1794,11 +1829,11 @@
         <v>42</v>
       </c>
       <c r="C12" s="1">
-        <v>2300</v>
+        <v>2650</v>
       </c>
       <c r="D12" s="1">
         <f t="shared" si="0"/>
-        <v>3300</v>
+        <v>3800</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -1810,11 +1845,11 @@
         <v>46</v>
       </c>
       <c r="C13" s="1">
-        <v>2300</v>
+        <v>2750</v>
       </c>
       <c r="D13" s="1">
         <f t="shared" si="0"/>
-        <v>3300</v>
+        <v>3900</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -1842,11 +1877,11 @@
         <v>52</v>
       </c>
       <c r="C15" s="1">
-        <v>1300</v>
+        <v>1400</v>
       </c>
       <c r="D15" s="1">
         <f t="shared" si="0"/>
-        <v>1900</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -1858,11 +1893,11 @@
         <v>61</v>
       </c>
       <c r="C16" s="1">
-        <v>2000</v>
+        <v>2100</v>
       </c>
       <c r="D16" s="1">
         <f t="shared" si="0"/>
-        <v>2800</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -1874,11 +1909,11 @@
         <v>64</v>
       </c>
       <c r="C17" s="1">
-        <v>1750</v>
+        <v>1950</v>
       </c>
       <c r="D17" s="1">
         <f t="shared" si="0"/>
-        <v>2500</v>
+        <v>2800</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -1890,11 +1925,11 @@
         <v>67</v>
       </c>
       <c r="C18" s="1">
-        <v>1300</v>
+        <v>1250</v>
       </c>
       <c r="D18" s="1">
         <f t="shared" si="0"/>
-        <v>1900</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -1906,11 +1941,11 @@
         <v>70</v>
       </c>
       <c r="C19" s="1">
-        <v>1750</v>
+        <v>1950</v>
       </c>
       <c r="D19" s="1">
         <f t="shared" si="0"/>
-        <v>2500</v>
+        <v>2800</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -1938,11 +1973,11 @@
         <v>77</v>
       </c>
       <c r="C21" s="1">
-        <v>2100</v>
+        <v>2250</v>
       </c>
       <c r="D21" s="1">
         <f t="shared" si="0"/>
-        <v>3000</v>
+        <v>3200</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -1951,14 +1986,14 @@
         <v>21</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>79</v>
+        <v>438</v>
       </c>
       <c r="C22" s="1">
-        <v>1750</v>
+        <v>1950</v>
       </c>
       <c r="D22" s="1">
         <f t="shared" si="0"/>
-        <v>2500</v>
+        <v>2800</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -1967,14 +2002,14 @@
         <v>22</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C23" s="1">
-        <v>2550</v>
+        <v>2600</v>
       </c>
       <c r="D23" s="1">
         <f t="shared" si="0"/>
-        <v>3600</v>
+        <v>3700</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -1983,7 +2018,7 @@
         <v>23</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C24" s="1">
         <v>2250</v>
@@ -1999,7 +2034,7 @@
         <v>24</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C25" s="1">
         <v>1550</v>
@@ -2015,7 +2050,7 @@
         <v>25</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C26" s="1">
         <v>2850</v>
@@ -2031,7 +2066,7 @@
         <v>26</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C27" s="1">
         <v>7100</v>
@@ -2047,7 +2082,7 @@
         <v>27</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C28" s="1">
         <v>2500</v>
@@ -2063,11 +2098,14 @@
         <v>28</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="D29" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
+        <v>104</v>
+      </c>
+      <c r="C29" s="3">
+        <v>4250</v>
+      </c>
+      <c r="D29" s="1">
+        <f t="shared" si="0"/>
+        <v>6000</v>
       </c>
     </row>
     <row r="30" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -2076,7 +2114,7 @@
         <v>29</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C30" s="1">
         <v>10650</v>
@@ -2092,7 +2130,7 @@
         <v>30</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C31" s="1">
         <v>2100</v>
@@ -2108,7 +2146,7 @@
         <v>31</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C32" s="1">
         <v>1800</v>
@@ -2124,7 +2162,7 @@
         <v>32</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C33" s="1">
         <v>1200</v>
@@ -2140,7 +2178,7 @@
         <v>33</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C34" s="1">
         <v>1500</v>
@@ -2156,7 +2194,7 @@
         <v>34</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C35" s="1">
         <v>1250</v>
@@ -2172,7 +2210,7 @@
         <v>35</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C36" s="1">
         <v>1250</v>
@@ -2188,7 +2226,7 @@
         <v>36</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C37" s="1">
         <v>1050</v>
@@ -2204,7 +2242,7 @@
         <v>37</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C38" s="1">
         <v>2800</v>
@@ -2220,7 +2258,7 @@
         <v>38</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C39" s="1">
         <v>3200</v>
@@ -2236,7 +2274,7 @@
         <v>39</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C40" s="1">
         <v>11400</v>
@@ -2252,7 +2290,7 @@
         <v>40</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C41" s="1">
         <v>9950</v>
@@ -2268,7 +2306,7 @@
         <v>41</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C42" s="1">
         <v>5350</v>
@@ -2284,7 +2322,7 @@
         <v>42</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C43" s="1">
         <v>1050</v>
@@ -2300,7 +2338,7 @@
         <v>43</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C44" s="1">
         <v>900</v>
@@ -2316,7 +2354,7 @@
         <v>44</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C45" s="1">
         <v>800</v>
@@ -2332,7 +2370,7 @@
         <v>45</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C46" s="1">
         <v>600</v>
@@ -2348,7 +2386,7 @@
         <v>46</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C47" s="1">
         <v>1400</v>
@@ -2364,7 +2402,7 @@
         <v>47</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C48" s="1">
         <v>1750</v>
@@ -2380,7 +2418,7 @@
         <v>48</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C49" s="1">
         <v>2800</v>
@@ -2396,7 +2434,7 @@
         <v>49</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="51" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -2405,7 +2443,7 @@
         <v>50</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C51" s="1">
         <v>1550</v>
@@ -2421,7 +2459,7 @@
         <v>51</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C52" s="1">
         <v>1750</v>
@@ -2437,7 +2475,7 @@
         <v>52</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D53" s="1" t="str">
         <f t="shared" si="2"/>
@@ -2450,7 +2488,7 @@
         <v>53</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C54" s="1">
         <v>3900</v>
@@ -2466,7 +2504,7 @@
         <v>54</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C55" s="1">
         <v>1400</v>
@@ -2482,7 +2520,7 @@
         <v>55</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C56" s="1">
         <v>700</v>
@@ -2498,7 +2536,7 @@
         <v>56</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C57" s="1">
         <v>1100</v>
@@ -2514,7 +2552,7 @@
         <v>57</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C58" s="1">
         <v>700</v>
@@ -2530,7 +2568,7 @@
         <v>58</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C59" s="1">
         <v>450</v>
@@ -2546,7 +2584,7 @@
         <v>59</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D60" s="1" t="str">
         <f t="shared" si="2"/>
@@ -2559,7 +2597,7 @@
         <v>60</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C61" s="1">
         <v>700</v>
@@ -2575,7 +2613,7 @@
         <v>61</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C62" s="1">
         <v>1400</v>
@@ -2591,7 +2629,7 @@
         <v>62</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C63" s="1">
         <v>700</v>
@@ -2607,7 +2645,7 @@
         <v>63</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C64" s="1">
         <v>2000</v>
@@ -2623,7 +2661,7 @@
         <v>64</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C65" s="1">
         <v>1550</v>
@@ -2639,7 +2677,7 @@
         <v>65</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C66" s="1">
         <v>1400</v>
@@ -2655,7 +2693,7 @@
         <v>66</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C67" s="1">
         <v>1250</v>
@@ -2671,14 +2709,14 @@
         <v>67</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C68" s="1">
-        <v>1750</v>
+        <v>1950</v>
       </c>
       <c r="D68" s="1">
         <f t="shared" si="2"/>
-        <v>2500</v>
+        <v>2800</v>
       </c>
     </row>
     <row r="69" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -2687,7 +2725,7 @@
         <v>68</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C69" s="1">
         <v>1400</v>
@@ -2703,7 +2741,7 @@
         <v>69</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C70" s="1">
         <v>1250</v>
@@ -2719,7 +2757,7 @@
         <v>70</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C71" s="1">
         <v>750</v>
@@ -2735,11 +2773,14 @@
         <v>71</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="D72" s="1" t="str">
+        <v>223</v>
+      </c>
+      <c r="C72" s="3">
+        <v>1400</v>
+      </c>
+      <c r="D72" s="1">
         <f t="shared" si="2"/>
-        <v/>
+        <v>2000</v>
       </c>
     </row>
     <row r="73" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -2748,14 +2789,14 @@
         <v>72</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C73" s="1">
-        <v>1350</v>
+        <v>1400</v>
       </c>
       <c r="D73" s="1">
         <f t="shared" si="2"/>
-        <v>1900</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="74" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -2764,7 +2805,7 @@
         <v>73</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C74" s="1">
         <v>1050</v>
@@ -2780,7 +2821,7 @@
         <v>74</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D75" s="1" t="str">
         <f t="shared" si="2"/>
@@ -2793,7 +2834,7 @@
         <v>75</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D76" s="1" t="str">
         <f t="shared" si="2"/>
@@ -2806,7 +2847,7 @@
         <v>76</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C77" s="1">
         <v>450</v>
@@ -2822,7 +2863,7 @@
         <v>77</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C78" s="1">
         <v>1050</v>
@@ -2838,7 +2879,7 @@
         <v>78</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C79" s="1">
         <v>1050</v>
@@ -2854,7 +2895,7 @@
         <v>79</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C80" s="1">
         <v>1400</v>
@@ -2870,7 +2911,7 @@
         <v>80</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C81" s="1">
         <v>1750</v>
@@ -2886,7 +2927,7 @@
         <v>81</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C82" s="1">
         <v>1050</v>
@@ -2902,7 +2943,7 @@
         <v>82</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C83" s="1">
         <v>1050</v>
@@ -2918,7 +2959,7 @@
         <v>83</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C84" s="1">
         <v>1400</v>
@@ -2934,7 +2975,7 @@
         <v>84</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C85" s="1">
         <v>700</v>
@@ -2950,7 +2991,7 @@
         <v>85</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C86" s="1">
         <v>1400</v>
@@ -2966,7 +3007,7 @@
         <v>86</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C87" s="1">
         <v>550</v>
@@ -2982,7 +3023,7 @@
         <v>87</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C88" s="1">
         <v>800</v>
@@ -2998,7 +3039,7 @@
         <v>88</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C89" s="1">
         <v>1050</v>
@@ -3014,7 +3055,7 @@
         <v>89</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C90" s="1">
         <v>1050</v>
@@ -3030,7 +3071,7 @@
         <v>90</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C91" s="1">
         <v>2500</v>
@@ -3046,7 +3087,7 @@
         <v>91</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C92" s="1">
         <v>800</v>
@@ -3062,7 +3103,7 @@
         <v>92</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C93" s="1">
         <v>1200</v>
@@ -3078,7 +3119,7 @@
         <v>93</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C94" s="1">
         <v>700</v>
@@ -3094,7 +3135,7 @@
         <v>94</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C95" s="1">
         <v>1400</v>
@@ -3110,14 +3151,14 @@
         <v>95</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C96" s="1">
-        <v>1200</v>
+        <v>1050</v>
       </c>
       <c r="D96" s="1">
         <f t="shared" si="2"/>
-        <v>1700</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="97" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -3126,7 +3167,7 @@
         <v>96</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C97" s="1">
         <v>1400</v>
@@ -3142,7 +3183,7 @@
         <v>97</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C98" s="1">
         <v>1050</v>
@@ -3158,7 +3199,7 @@
         <v>98</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C99" s="1">
         <v>600</v>
@@ -3174,7 +3215,7 @@
         <v>99</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C100" s="1">
         <v>1050</v>
@@ -3190,14 +3231,14 @@
         <v>100</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C101" s="1">
-        <v>3500</v>
+        <v>4100</v>
       </c>
       <c r="D101" s="1">
         <f t="shared" si="2"/>
-        <v>4900</v>
+        <v>5800</v>
       </c>
     </row>
     <row r="102" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -3206,7 +3247,7 @@
         <v>101</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C102" s="1">
         <v>1750</v>
@@ -3222,14 +3263,14 @@
         <v>102</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C103" s="1">
-        <v>1600</v>
+        <v>1750</v>
       </c>
       <c r="D103" s="1">
         <f t="shared" si="2"/>
-        <v>2300</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="104" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -3238,7 +3279,7 @@
         <v>103</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C104" s="1">
         <v>600</v>
@@ -3254,14 +3295,14 @@
         <v>104</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C105" s="1">
-        <v>2000</v>
+        <v>2250</v>
       </c>
       <c r="D105" s="1">
         <f t="shared" si="2"/>
-        <v>2800</v>
+        <v>3200</v>
       </c>
     </row>
     <row r="106" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -3270,14 +3311,14 @@
         <v>105</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C106" s="1">
-        <v>2250</v>
+        <v>2600</v>
       </c>
       <c r="D106" s="1">
         <f t="shared" si="2"/>
-        <v>3200</v>
+        <v>3700</v>
       </c>
     </row>
     <row r="107" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -3286,7 +3327,7 @@
         <v>106</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C107" s="1">
         <v>1100</v>
@@ -3302,14 +3343,14 @@
         <v>107</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C108" s="1">
-        <v>1000</v>
+        <v>1050</v>
       </c>
       <c r="D108" s="1">
         <f t="shared" si="2"/>
-        <v>1400</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="109" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -3318,7 +3359,7 @@
         <v>108</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C109" s="1">
         <v>1050</v>
@@ -3334,7 +3375,7 @@
         <v>109</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C110" s="1">
         <v>1400</v>
@@ -3350,7 +3391,7 @@
         <v>110</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C111" s="1">
         <v>2100</v>
@@ -3366,7 +3407,7 @@
         <v>111</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C112" s="1">
         <v>1600</v>
@@ -3382,7 +3423,7 @@
         <v>112</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C113" s="1">
         <v>1750</v>
@@ -3398,7 +3439,7 @@
         <v>113</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C114" s="1">
         <v>900</v>
@@ -3414,7 +3455,7 @@
         <v>114</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C115" s="1">
         <v>1200</v>
@@ -3430,7 +3471,7 @@
         <v>115</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C116" s="1">
         <v>1200</v>
@@ -3446,7 +3487,7 @@
         <v>116</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C117" s="1">
         <v>200</v>
@@ -3462,7 +3503,7 @@
         <v>117</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C118" s="1">
         <v>1400</v>
@@ -3478,7 +3519,7 @@
         <v>118</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C119" s="1">
         <v>900</v>
@@ -3494,7 +3535,7 @@
         <v>119</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C120" s="1">
         <v>1250</v>
@@ -3510,11 +3551,14 @@
         <v>120</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>315</v>
-      </c>
-      <c r="D121" s="1" t="str">
+        <v>314</v>
+      </c>
+      <c r="C121" s="3">
+        <v>1750</v>
+      </c>
+      <c r="D121" s="1">
         <f t="shared" si="2"/>
-        <v/>
+        <v>2500</v>
       </c>
     </row>
     <row r="122" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -3523,7 +3567,7 @@
         <v>121</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C122" s="1">
         <v>1100</v>
@@ -3539,14 +3583,14 @@
         <v>122</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C123" s="1">
-        <v>2250</v>
+        <v>2300</v>
       </c>
       <c r="D123" s="1">
         <f t="shared" si="2"/>
-        <v>3200</v>
+        <v>3300</v>
       </c>
     </row>
     <row r="124" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -3555,14 +3599,14 @@
         <v>123</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C124" s="1">
-        <v>1550</v>
+        <v>1750</v>
       </c>
       <c r="D124" s="1">
         <f t="shared" si="2"/>
-        <v>2200</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="125" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -3571,7 +3615,7 @@
         <v>124</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C125" s="1">
         <v>2450</v>
@@ -3587,7 +3631,7 @@
         <v>125</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C126" s="1">
         <v>250</v>
@@ -3603,7 +3647,7 @@
         <v>126</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C127" s="1">
         <v>2300</v>
@@ -3619,7 +3663,7 @@
         <v>127</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="D128" s="1">
         <v>150</v>
@@ -3631,7 +3675,7 @@
         <v>128</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="D129" s="1">
         <v>150</v>
@@ -3643,10 +3687,10 @@
         <v>129</v>
       </c>
       <c r="B130" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="C130" s="1" t="s">
         <v>325</v>
-      </c>
-      <c r="C130" s="1" t="s">
-        <v>326</v>
       </c>
       <c r="D130" s="1">
         <v>150</v>
@@ -3658,7 +3702,7 @@
         <v>130</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="D131" s="1">
         <v>200</v>
@@ -3670,7 +3714,7 @@
         <v>131</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="D132" s="1">
         <v>100</v>
@@ -3682,7 +3726,7 @@
         <v>132</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="D133" s="1">
         <v>100</v>
@@ -3694,7 +3738,7 @@
         <v>133</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C134" s="1">
         <v>1750</v>
@@ -3710,14 +3754,14 @@
         <v>134</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C135" s="1">
-        <v>1600</v>
+        <v>1650</v>
       </c>
       <c r="D135" s="1">
         <f t="shared" si="3"/>
-        <v>2300</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="136" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -3726,14 +3770,14 @@
         <v>135</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C136" s="1">
-        <v>550</v>
+        <v>600</v>
       </c>
       <c r="D136" s="1">
         <f t="shared" si="3"/>
-        <v>800</v>
+        <v>900</v>
       </c>
     </row>
     <row r="137" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -3742,14 +3786,14 @@
         <v>136</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C137" s="1">
-        <v>1300</v>
+        <v>1450</v>
       </c>
       <c r="D137" s="1">
         <f t="shared" si="3"/>
-        <v>1900</v>
+        <v>2100</v>
       </c>
     </row>
     <row r="138" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -3758,14 +3802,14 @@
         <v>137</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C138" s="1">
-        <v>500</v>
+        <v>550</v>
       </c>
       <c r="D138" s="1">
         <f t="shared" si="3"/>
-        <v>700</v>
+        <v>800</v>
       </c>
     </row>
     <row r="139" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -3774,14 +3818,14 @@
         <v>138</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C139" s="1">
-        <v>900</v>
+        <v>1200</v>
       </c>
       <c r="D139" s="1">
         <f t="shared" si="3"/>
-        <v>1300</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="140" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -3790,46 +3834,68 @@
         <v>139</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C140" s="1">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="D140" s="1">
         <f t="shared" si="3"/>
-        <v>500</v>
+        <v>600</v>
       </c>
     </row>
     <row r="141" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D141" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A141" s="1">
+        <f t="shared" ref="A141:A145" si="4">IF(B140&lt;&gt;"", A140+1, "")</f>
+        <v>140</v>
+      </c>
+      <c r="B141" s="3" t="s">
+        <v>439</v>
+      </c>
+      <c r="C141" s="3">
+        <v>1750</v>
+      </c>
+      <c r="D141" s="1">
+        <f t="shared" si="3"/>
+        <v>2500</v>
       </c>
     </row>
     <row r="142" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A142" s="1" t="str">
-        <f t="shared" ref="A142:A396" si="4">IF(B141&lt;&gt;"", A141+1, "")</f>
-        <v/>
-      </c>
-      <c r="D142" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A142" s="1">
+        <f t="shared" si="4"/>
+        <v>141</v>
+      </c>
+      <c r="B142" s="3" t="s">
+        <v>441</v>
+      </c>
+      <c r="C142" s="3">
+        <v>1400</v>
+      </c>
+      <c r="D142" s="1">
+        <f t="shared" si="3"/>
+        <v>2000</v>
       </c>
     </row>
     <row r="143" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A143" s="1" t="str">
+      <c r="A143" s="1">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="D143" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+        <v>142</v>
+      </c>
+      <c r="B143" s="3" t="s">
+        <v>442</v>
+      </c>
+      <c r="C143" s="3">
+        <v>1550</v>
+      </c>
+      <c r="D143" s="1">
+        <f t="shared" si="3"/>
+        <v>2200</v>
       </c>
     </row>
     <row r="144" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A144" s="1" t="str">
+      <c r="A144" s="1">
         <f t="shared" si="4"/>
-        <v/>
+        <v>143</v>
       </c>
       <c r="D144" s="1" t="str">
         <f t="shared" si="3"/>
@@ -3848,7 +3914,7 @@
     </row>
     <row r="146" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A146" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" ref="A142:A396" si="5">IF(B145&lt;&gt;"", A145+1, "")</f>
         <v/>
       </c>
       <c r="D146" s="1" t="str">
@@ -3858,7 +3924,7 @@
     </row>
     <row r="147" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A147" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D147" s="1" t="str">
@@ -3868,7 +3934,7 @@
     </row>
     <row r="148" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A148" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D148" s="1" t="str">
@@ -3878,7 +3944,7 @@
     </row>
     <row r="149" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A149" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D149" s="1" t="str">
@@ -3888,7 +3954,7 @@
     </row>
     <row r="150" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A150" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D150" s="1" t="str">
@@ -3898,7 +3964,7 @@
     </row>
     <row r="151" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A151" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D151" s="1" t="str">
@@ -3908,7 +3974,7 @@
     </row>
     <row r="152" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A152" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D152" s="1" t="str">
@@ -3918,7 +3984,7 @@
     </row>
     <row r="153" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A153" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D153" s="1" t="str">
@@ -3928,7 +3994,7 @@
     </row>
     <row r="154" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A154" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D154" s="1" t="str">
@@ -3938,7 +4004,7 @@
     </row>
     <row r="155" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A155" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D155" s="1" t="str">
@@ -3948,7 +4014,7 @@
     </row>
     <row r="156" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A156" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D156" s="1" t="str">
@@ -3958,7 +4024,7 @@
     </row>
     <row r="157" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A157" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D157" s="1" t="str">
@@ -3968,7 +4034,7 @@
     </row>
     <row r="158" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A158" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D158" s="1" t="str">
@@ -3978,7 +4044,7 @@
     </row>
     <row r="159" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A159" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D159" s="1" t="str">
@@ -3988,7 +4054,7 @@
     </row>
     <row r="160" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A160" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D160" s="1" t="str">
@@ -3998,7 +4064,7 @@
     </row>
     <row r="161" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A161" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D161" s="1" t="str">
@@ -4008,7 +4074,7 @@
     </row>
     <row r="162" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A162" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D162" s="1" t="str">
@@ -4018,7 +4084,7 @@
     </row>
     <row r="163" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A163" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D163" s="1" t="str">
@@ -4028,7 +4094,7 @@
     </row>
     <row r="164" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A164" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D164" s="1" t="str">
@@ -4038,7 +4104,7 @@
     </row>
     <row r="165" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A165" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D165" s="1" t="str">
@@ -4048,7 +4114,7 @@
     </row>
     <row r="166" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A166" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D166" s="1" t="str">
@@ -4058,7 +4124,7 @@
     </row>
     <row r="167" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A167" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D167" s="1" t="str">
@@ -4068,7 +4134,7 @@
     </row>
     <row r="168" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A168" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D168" s="1" t="str">
@@ -4078,7 +4144,7 @@
     </row>
     <row r="169" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A169" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D169" s="1" t="str">
@@ -4088,7 +4154,7 @@
     </row>
     <row r="170" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A170" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D170" s="1" t="str">
@@ -4098,7 +4164,7 @@
     </row>
     <row r="171" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A171" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D171" s="1" t="str">
@@ -4108,7 +4174,7 @@
     </row>
     <row r="172" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A172" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D172" s="1" t="str">
@@ -4118,7 +4184,7 @@
     </row>
     <row r="173" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A173" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D173" s="1" t="str">
@@ -4128,7 +4194,7 @@
     </row>
     <row r="174" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A174" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D174" s="1" t="str">
@@ -4138,7 +4204,7 @@
     </row>
     <row r="175" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A175" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D175" s="1" t="str">
@@ -4148,7 +4214,7 @@
     </row>
     <row r="176" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A176" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D176" s="1" t="str">
@@ -4158,7 +4224,7 @@
     </row>
     <row r="177" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A177" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D177" s="1" t="str">
@@ -4168,7 +4234,7 @@
     </row>
     <row r="178" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A178" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D178" s="1" t="str">
@@ -4178,7 +4244,7 @@
     </row>
     <row r="179" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A179" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D179" s="1" t="str">
@@ -4188,7 +4254,7 @@
     </row>
     <row r="180" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A180" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D180" s="1" t="str">
@@ -4198,7 +4264,7 @@
     </row>
     <row r="181" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A181" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D181" s="1" t="str">
@@ -4208,7 +4274,7 @@
     </row>
     <row r="182" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A182" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D182" s="1" t="str">
@@ -4218,7 +4284,7 @@
     </row>
     <row r="183" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A183" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D183" s="1" t="str">
@@ -4228,7 +4294,7 @@
     </row>
     <row r="184" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A184" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D184" s="1" t="str">
@@ -4238,7 +4304,7 @@
     </row>
     <row r="185" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A185" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D185" s="1" t="str">
@@ -4248,7 +4314,7 @@
     </row>
     <row r="186" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A186" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D186" s="1" t="str">
@@ -4258,7 +4324,7 @@
     </row>
     <row r="187" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A187" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D187" s="1" t="str">
@@ -4268,7 +4334,7 @@
     </row>
     <row r="188" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A188" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D188" s="1" t="str">
@@ -4278,7 +4344,7 @@
     </row>
     <row r="189" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A189" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D189" s="1" t="str">
@@ -4288,7 +4354,7 @@
     </row>
     <row r="190" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A190" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D190" s="1" t="str">
@@ -4298,7 +4364,7 @@
     </row>
     <row r="191" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A191" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D191" s="1" t="str">
@@ -4308,7 +4374,7 @@
     </row>
     <row r="192" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A192" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D192" s="1" t="str">
@@ -4318,7 +4384,7 @@
     </row>
     <row r="193" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A193" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D193" s="1" t="str">
@@ -4328,7 +4394,7 @@
     </row>
     <row r="194" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A194" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D194" s="1" t="str">
@@ -4338,7 +4404,7 @@
     </row>
     <row r="195" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A195" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D195" s="1" t="str">
@@ -4348,7 +4414,7 @@
     </row>
     <row r="196" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A196" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D196" s="1" t="str">
@@ -4358,7 +4424,7 @@
     </row>
     <row r="197" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A197" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D197" s="1" t="str">
@@ -4368,7 +4434,7 @@
     </row>
     <row r="198" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A198" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D198" s="1" t="str">
@@ -4378,7 +4444,7 @@
     </row>
     <row r="199" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A199" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D199" s="1" t="str">
@@ -4388,7 +4454,7 @@
     </row>
     <row r="200" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A200" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D200" s="1" t="str">
@@ -4398,7 +4464,7 @@
     </row>
     <row r="201" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A201" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D201" s="1" t="str">
@@ -4408,7 +4474,7 @@
     </row>
     <row r="202" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A202" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D202" s="1" t="str">
@@ -4418,7 +4484,7 @@
     </row>
     <row r="203" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A203" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D203" s="1" t="str">
@@ -4428,7 +4494,7 @@
     </row>
     <row r="204" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A204" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D204" s="1" t="str">
@@ -4438,7 +4504,7 @@
     </row>
     <row r="205" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A205" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D205" s="1" t="str">
@@ -4448,7 +4514,7 @@
     </row>
     <row r="206" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A206" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D206" s="1" t="str">
@@ -4458,7 +4524,7 @@
     </row>
     <row r="207" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A207" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D207" s="1" t="str">
@@ -4468,7 +4534,7 @@
     </row>
     <row r="208" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A208" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D208" s="1" t="str">
@@ -4478,7 +4544,7 @@
     </row>
     <row r="209" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A209" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D209" s="1" t="str">
@@ -4488,7 +4554,7 @@
     </row>
     <row r="210" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A210" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D210" s="1" t="str">
@@ -4498,7 +4564,7 @@
     </row>
     <row r="211" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A211" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D211" s="1" t="str">
@@ -4508,7 +4574,7 @@
     </row>
     <row r="212" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A212" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D212" s="1" t="str">
@@ -4518,7 +4584,7 @@
     </row>
     <row r="213" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A213" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D213" s="1" t="str">
@@ -4528,7 +4594,7 @@
     </row>
     <row r="214" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A214" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D214" s="1" t="str">
@@ -4538,7 +4604,7 @@
     </row>
     <row r="215" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A215" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D215" s="1" t="str">
@@ -4548,7 +4614,7 @@
     </row>
     <row r="216" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A216" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D216" s="1" t="str">
@@ -4558,7 +4624,7 @@
     </row>
     <row r="217" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A217" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D217" s="1" t="str">
@@ -4568,7 +4634,7 @@
     </row>
     <row r="218" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A218" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D218" s="1" t="str">
@@ -4578,7 +4644,7 @@
     </row>
     <row r="219" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A219" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D219" s="1" t="str">
@@ -4588,7 +4654,7 @@
     </row>
     <row r="220" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A220" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D220" s="1" t="str">
@@ -4598,7 +4664,7 @@
     </row>
     <row r="221" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A221" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D221" s="1" t="str">
@@ -4608,7 +4674,7 @@
     </row>
     <row r="222" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A222" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D222" s="1" t="str">
@@ -4618,7 +4684,7 @@
     </row>
     <row r="223" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A223" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D223" s="1" t="str">
@@ -4628,7 +4694,7 @@
     </row>
     <row r="224" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A224" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D224" s="1" t="str">
@@ -4638,7 +4704,7 @@
     </row>
     <row r="225" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A225" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D225" s="1" t="str">
@@ -4648,7 +4714,7 @@
     </row>
     <row r="226" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A226" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D226" s="1" t="str">
@@ -4658,7 +4724,7 @@
     </row>
     <row r="227" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A227" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D227" s="1" t="str">
@@ -4668,7 +4734,7 @@
     </row>
     <row r="228" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A228" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D228" s="1" t="str">
@@ -4678,7 +4744,7 @@
     </row>
     <row r="229" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A229" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D229" s="1" t="str">
@@ -4688,7 +4754,7 @@
     </row>
     <row r="230" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A230" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D230" s="1" t="str">
@@ -4698,7 +4764,7 @@
     </row>
     <row r="231" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A231" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D231" s="1" t="str">
@@ -4708,7 +4774,7 @@
     </row>
     <row r="232" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A232" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D232" s="1" t="str">
@@ -4718,7 +4784,7 @@
     </row>
     <row r="233" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A233" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D233" s="1" t="str">
@@ -4728,7 +4794,7 @@
     </row>
     <row r="234" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A234" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D234" s="1" t="str">
@@ -4738,7 +4804,7 @@
     </row>
     <row r="235" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A235" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D235" s="1" t="str">
@@ -4748,7 +4814,7 @@
     </row>
     <row r="236" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A236" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D236" s="1" t="str">
@@ -4758,7 +4824,7 @@
     </row>
     <row r="237" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A237" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D237" s="1" t="str">
@@ -4768,7 +4834,7 @@
     </row>
     <row r="238" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A238" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D238" s="1" t="str">
@@ -4778,7 +4844,7 @@
     </row>
     <row r="239" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A239" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D239" s="1" t="str">
@@ -4788,7 +4854,7 @@
     </row>
     <row r="240" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A240" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D240" s="1" t="str">
@@ -4798,7 +4864,7 @@
     </row>
     <row r="241" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A241" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D241" s="1" t="str">
@@ -4808,7 +4874,7 @@
     </row>
     <row r="242" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A242" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D242" s="1" t="str">
@@ -4818,7 +4884,7 @@
     </row>
     <row r="243" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A243" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D243" s="1" t="str">
@@ -4828,7 +4894,7 @@
     </row>
     <row r="244" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A244" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D244" s="1" t="str">
@@ -4838,7 +4904,7 @@
     </row>
     <row r="245" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A245" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D245" s="1" t="str">
@@ -4848,7 +4914,7 @@
     </row>
     <row r="246" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A246" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D246" s="1" t="str">
@@ -4858,7 +4924,7 @@
     </row>
     <row r="247" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A247" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D247" s="1" t="str">
@@ -4868,7 +4934,7 @@
     </row>
     <row r="248" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A248" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D248" s="1" t="str">
@@ -4878,7 +4944,7 @@
     </row>
     <row r="249" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A249" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D249" s="1" t="str">
@@ -4888,7 +4954,7 @@
     </row>
     <row r="250" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A250" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D250" s="1" t="str">
@@ -4898,7 +4964,7 @@
     </row>
     <row r="251" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A251" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D251" s="1" t="str">
@@ -4908,7 +4974,7 @@
     </row>
     <row r="252" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A252" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D252" s="1" t="str">
@@ -4918,7 +4984,7 @@
     </row>
     <row r="253" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A253" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D253" s="1" t="str">
@@ -4928,7 +4994,7 @@
     </row>
     <row r="254" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A254" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D254" s="1" t="str">
@@ -4938,7 +5004,7 @@
     </row>
     <row r="255" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A255" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D255" s="1" t="str">
@@ -4948,7 +5014,7 @@
     </row>
     <row r="256" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A256" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D256" s="1" t="str">
@@ -4958,7 +5024,7 @@
     </row>
     <row r="257" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A257" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D257" s="1" t="str">
@@ -4968,7 +5034,7 @@
     </row>
     <row r="258" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A258" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D258" s="1" t="str">
@@ -4978,7 +5044,7 @@
     </row>
     <row r="259" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A259" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D259" s="1" t="str">
@@ -4988,7 +5054,7 @@
     </row>
     <row r="260" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A260" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D260" s="1" t="str">
@@ -4998,7 +5064,7 @@
     </row>
     <row r="261" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A261" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D261" s="1" t="str">
@@ -5008,7 +5074,7 @@
     </row>
     <row r="262" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A262" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D262" s="1" t="str">
@@ -5018,7 +5084,7 @@
     </row>
     <row r="263" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A263" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D263" s="1" t="str">
@@ -5028,7 +5094,7 @@
     </row>
     <row r="264" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A264" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D264" s="1" t="str">
@@ -5038,7 +5104,7 @@
     </row>
     <row r="265" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A265" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D265" s="1" t="str">
@@ -5048,7 +5114,7 @@
     </row>
     <row r="266" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A266" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D266" s="1" t="str">
@@ -5058,7 +5124,7 @@
     </row>
     <row r="267" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A267" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D267" s="1" t="str">
@@ -5068,7 +5134,7 @@
     </row>
     <row r="268" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A268" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D268" s="1" t="str">
@@ -5078,7 +5144,7 @@
     </row>
     <row r="269" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A269" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D269" s="1" t="str">
@@ -5088,7 +5154,7 @@
     </row>
     <row r="270" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A270" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D270" s="1" t="str">
@@ -5098,7 +5164,7 @@
     </row>
     <row r="271" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A271" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D271" s="1" t="str">
@@ -5108,7 +5174,7 @@
     </row>
     <row r="272" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A272" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D272" s="1" t="str">
@@ -5118,7 +5184,7 @@
     </row>
     <row r="273" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A273" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D273" s="1" t="str">
@@ -5128,7 +5194,7 @@
     </row>
     <row r="274" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A274" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D274" s="1" t="str">
@@ -5138,7 +5204,7 @@
     </row>
     <row r="275" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A275" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D275" s="1" t="str">
@@ -5148,7 +5214,7 @@
     </row>
     <row r="276" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A276" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D276" s="1" t="str">
@@ -5158,7 +5224,7 @@
     </row>
     <row r="277" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A277" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D277" s="1" t="str">
@@ -5168,7 +5234,7 @@
     </row>
     <row r="278" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A278" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D278" s="1" t="str">
@@ -5178,7 +5244,7 @@
     </row>
     <row r="279" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A279" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D279" s="1" t="str">
@@ -5188,7 +5254,7 @@
     </row>
     <row r="280" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A280" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D280" s="1" t="str">
@@ -5198,7 +5264,7 @@
     </row>
     <row r="281" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A281" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D281" s="1" t="str">
@@ -5208,7 +5274,7 @@
     </row>
     <row r="282" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A282" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D282" s="1" t="str">
@@ -5218,7 +5284,7 @@
     </row>
     <row r="283" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A283" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D283" s="1" t="str">
@@ -5228,7 +5294,7 @@
     </row>
     <row r="284" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A284" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D284" s="1" t="str">
@@ -5238,7 +5304,7 @@
     </row>
     <row r="285" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A285" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D285" s="1" t="str">
@@ -5248,7 +5314,7 @@
     </row>
     <row r="286" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A286" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D286" s="1" t="str">
@@ -5258,7 +5324,7 @@
     </row>
     <row r="287" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A287" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D287" s="1" t="str">
@@ -5268,7 +5334,7 @@
     </row>
     <row r="288" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A288" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D288" s="1" t="str">
@@ -5278,7 +5344,7 @@
     </row>
     <row r="289" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A289" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D289" s="1" t="str">
@@ -5288,7 +5354,7 @@
     </row>
     <row r="290" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A290" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D290" s="1" t="str">
@@ -5298,7 +5364,7 @@
     </row>
     <row r="291" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A291" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D291" s="1" t="str">
@@ -5308,7 +5374,7 @@
     </row>
     <row r="292" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A292" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D292" s="1" t="str">
@@ -5318,7 +5384,7 @@
     </row>
     <row r="293" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A293" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D293" s="1" t="str">
@@ -5328,7 +5394,7 @@
     </row>
     <row r="294" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A294" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D294" s="1" t="str">
@@ -5338,7 +5404,7 @@
     </row>
     <row r="295" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A295" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D295" s="1" t="str">
@@ -5348,7 +5414,7 @@
     </row>
     <row r="296" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A296" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D296" s="1" t="str">
@@ -5358,7 +5424,7 @@
     </row>
     <row r="297" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A297" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D297" s="1" t="str">
@@ -5368,7 +5434,7 @@
     </row>
     <row r="298" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A298" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D298" s="1" t="str">
@@ -5378,7 +5444,7 @@
     </row>
     <row r="299" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A299" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D299" s="1" t="str">
@@ -5388,7 +5454,7 @@
     </row>
     <row r="300" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A300" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D300" s="1" t="str">
@@ -5398,7 +5464,7 @@
     </row>
     <row r="301" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A301" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D301" s="1" t="str">
@@ -5408,7 +5474,7 @@
     </row>
     <row r="302" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A302" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D302" s="1" t="str">
@@ -5418,7 +5484,7 @@
     </row>
     <row r="303" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A303" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D303" s="1" t="str">
@@ -5428,7 +5494,7 @@
     </row>
     <row r="304" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A304" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D304" s="1" t="str">
@@ -5438,7 +5504,7 @@
     </row>
     <row r="305" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A305" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D305" s="1" t="str">
@@ -5448,7 +5514,7 @@
     </row>
     <row r="306" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A306" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D306" s="1" t="str">
@@ -5458,7 +5524,7 @@
     </row>
     <row r="307" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A307" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D307" s="1" t="str">
@@ -5468,7 +5534,7 @@
     </row>
     <row r="308" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A308" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D308" s="1" t="str">
@@ -5478,7 +5544,7 @@
     </row>
     <row r="309" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A309" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D309" s="1" t="str">
@@ -5488,7 +5554,7 @@
     </row>
     <row r="310" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A310" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D310" s="1" t="str">
@@ -5498,7 +5564,7 @@
     </row>
     <row r="311" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A311" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D311" s="1" t="str">
@@ -5508,7 +5574,7 @@
     </row>
     <row r="312" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A312" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D312" s="1" t="str">
@@ -5518,7 +5584,7 @@
     </row>
     <row r="313" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A313" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D313" s="1" t="str">
@@ -5528,7 +5594,7 @@
     </row>
     <row r="314" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A314" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D314" s="1" t="str">
@@ -5538,7 +5604,7 @@
     </row>
     <row r="315" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A315" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D315" s="1" t="str">
@@ -5548,7 +5614,7 @@
     </row>
     <row r="316" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A316" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D316" s="1" t="str">
@@ -5558,7 +5624,7 @@
     </row>
     <row r="317" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A317" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D317" s="1" t="str">
@@ -5568,7 +5634,7 @@
     </row>
     <row r="318" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A318" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D318" s="1" t="str">
@@ -5578,7 +5644,7 @@
     </row>
     <row r="319" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A319" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D319" s="1" t="str">
@@ -5588,7 +5654,7 @@
     </row>
     <row r="320" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A320" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D320" s="1" t="str">
@@ -5598,7 +5664,7 @@
     </row>
     <row r="321" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A321" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D321" s="1" t="str">
@@ -5608,7 +5674,7 @@
     </row>
     <row r="322" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A322" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D322" s="1" t="str">
@@ -5618,7 +5684,7 @@
     </row>
     <row r="323" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A323" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D323" s="1" t="str">
@@ -5628,7 +5694,7 @@
     </row>
     <row r="324" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A324" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D324" s="1" t="str">
@@ -5638,7 +5704,7 @@
     </row>
     <row r="325" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A325" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D325" s="1" t="str">
@@ -5648,7 +5714,7 @@
     </row>
     <row r="326" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A326" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D326" s="1" t="str">
@@ -5658,7 +5724,7 @@
     </row>
     <row r="327" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A327" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D327" s="1" t="str">
@@ -5668,7 +5734,7 @@
     </row>
     <row r="328" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A328" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D328" s="1" t="str">
@@ -5678,7 +5744,7 @@
     </row>
     <row r="329" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A329" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D329" s="1" t="str">
@@ -5688,7 +5754,7 @@
     </row>
     <row r="330" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A330" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D330" s="1" t="str">
@@ -5698,7 +5764,7 @@
     </row>
     <row r="331" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A331" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D331" s="1" t="str">
@@ -5708,7 +5774,7 @@
     </row>
     <row r="332" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A332" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D332" s="1" t="str">
@@ -5718,7 +5784,7 @@
     </row>
     <row r="333" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A333" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D333" s="1" t="str">
@@ -5728,7 +5794,7 @@
     </row>
     <row r="334" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A334" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D334" s="1" t="str">
@@ -5738,7 +5804,7 @@
     </row>
     <row r="335" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A335" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D335" s="1" t="str">
@@ -5748,7 +5814,7 @@
     </row>
     <row r="336" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A336" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D336" s="1" t="str">
@@ -5758,7 +5824,7 @@
     </row>
     <row r="337" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A337" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D337" s="1" t="str">
@@ -5768,7 +5834,7 @@
     </row>
     <row r="338" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A338" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D338" s="1" t="str">
@@ -5778,7 +5844,7 @@
     </row>
     <row r="339" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A339" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D339" s="1" t="str">
@@ -5788,7 +5854,7 @@
     </row>
     <row r="340" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A340" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D340" s="1" t="str">
@@ -5798,7 +5864,7 @@
     </row>
     <row r="341" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A341" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D341" s="1" t="str">
@@ -5808,7 +5874,7 @@
     </row>
     <row r="342" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A342" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D342" s="1" t="str">
@@ -5818,7 +5884,7 @@
     </row>
     <row r="343" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A343" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D343" s="1" t="str">
@@ -5828,7 +5894,7 @@
     </row>
     <row r="344" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A344" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D344" s="1" t="str">
@@ -5838,7 +5904,7 @@
     </row>
     <row r="345" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A345" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D345" s="1" t="str">
@@ -5848,7 +5914,7 @@
     </row>
     <row r="346" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A346" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D346" s="1" t="str">
@@ -5858,7 +5924,7 @@
     </row>
     <row r="347" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A347" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D347" s="1" t="str">
@@ -5868,7 +5934,7 @@
     </row>
     <row r="348" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A348" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D348" s="1" t="str">
@@ -5878,7 +5944,7 @@
     </row>
     <row r="349" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A349" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D349" s="1" t="str">
@@ -5888,7 +5954,7 @@
     </row>
     <row r="350" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A350" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D350" s="1" t="str">
@@ -5898,7 +5964,7 @@
     </row>
     <row r="351" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A351" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D351" s="1" t="str">
@@ -5908,7 +5974,7 @@
     </row>
     <row r="352" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A352" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D352" s="1" t="str">
@@ -5918,7 +5984,7 @@
     </row>
     <row r="353" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A353" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D353" s="1" t="str">
@@ -5928,7 +5994,7 @@
     </row>
     <row r="354" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A354" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D354" s="1" t="str">
@@ -5938,7 +6004,7 @@
     </row>
     <row r="355" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A355" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D355" s="1" t="str">
@@ -5948,7 +6014,7 @@
     </row>
     <row r="356" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A356" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D356" s="1" t="str">
@@ -5958,7 +6024,7 @@
     </row>
     <row r="357" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A357" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D357" s="1" t="str">
@@ -5968,7 +6034,7 @@
     </row>
     <row r="358" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A358" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D358" s="1" t="str">
@@ -5978,7 +6044,7 @@
     </row>
     <row r="359" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A359" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D359" s="1" t="str">
@@ -5988,7 +6054,7 @@
     </row>
     <row r="360" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A360" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D360" s="1" t="str">
@@ -5998,7 +6064,7 @@
     </row>
     <row r="361" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A361" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D361" s="1" t="str">
@@ -6008,7 +6074,7 @@
     </row>
     <row r="362" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A362" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D362" s="1" t="str">
@@ -6018,7 +6084,7 @@
     </row>
     <row r="363" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A363" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="D363" s="1" t="str">
@@ -6028,2011 +6094,2011 @@
     </row>
     <row r="364" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A364" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="365" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A365" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="366" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A366" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="367" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A367" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="368" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A368" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="369" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A369" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="370" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A370" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="371" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A371" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="372" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A372" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="373" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A373" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="374" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A374" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="375" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A375" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="376" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A376" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="377" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A377" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="378" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A378" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="379" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A379" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="380" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A380" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="381" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A381" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="382" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A382" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="383" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A383" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="384" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A384" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="385" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A385" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="386" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A386" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="387" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A387" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="388" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A388" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="389" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A389" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="390" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A390" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="391" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A391" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="392" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A392" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="393" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A393" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="394" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A394" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="395" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A395" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="396" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A396" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="397" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A397" s="1" t="str">
-        <f t="shared" ref="A397:A651" si="5">IF(B396&lt;&gt;"", A396+1, "")</f>
+        <f t="shared" ref="A397:A651" si="6">IF(B396&lt;&gt;"", A396+1, "")</f>
         <v/>
       </c>
     </row>
     <row r="398" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A398" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="399" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A399" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="400" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A400" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="401" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A401" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="402" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A402" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="403" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A403" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="404" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A404" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="405" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A405" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="406" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A406" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="407" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A407" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="408" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A408" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="409" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A409" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="410" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A410" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="411" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A411" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="412" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A412" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="413" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A413" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="414" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A414" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="415" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A415" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="416" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A416" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="417" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A417" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="418" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A418" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="419" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A419" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="420" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A420" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="421" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A421" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="422" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A422" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="423" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A423" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="424" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A424" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="425" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A425" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="426" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A426" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="427" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A427" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="428" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A428" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="429" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A429" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="430" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A430" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="431" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A431" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="432" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A432" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="433" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A433" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="434" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A434" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="435" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A435" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="436" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A436" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="437" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A437" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="438" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A438" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="439" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A439" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="440" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A440" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="441" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A441" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="442" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A442" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="443" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A443" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="444" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A444" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="445" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A445" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="446" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A446" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="447" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A447" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="448" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A448" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="449" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A449" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="450" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A450" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="451" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A451" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="452" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A452" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="453" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A453" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="454" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A454" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="455" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A455" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="456" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A456" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="457" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A457" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="458" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A458" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="459" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A459" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="460" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A460" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="461" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A461" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="462" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A462" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="463" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A463" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="464" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A464" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="465" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A465" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="466" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A466" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="467" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A467" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="468" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A468" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="469" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A469" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="470" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A470" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="471" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A471" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="472" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A472" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="473" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A473" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="474" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A474" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="475" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A475" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="476" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A476" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="477" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A477" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="478" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A478" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="479" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A479" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="480" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A480" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="481" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A481" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="482" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A482" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="483" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A483" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="484" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A484" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="485" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A485" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="486" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A486" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="487" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A487" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="488" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A488" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="489" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A489" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="490" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A490" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="491" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A491" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="492" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A492" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="493" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A493" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="494" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A494" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="495" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A495" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="496" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A496" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="497" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A497" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="498" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A498" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="499" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A499" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="500" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A500" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="501" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A501" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="502" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A502" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="503" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A503" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="504" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A504" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="505" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A505" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="506" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A506" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="507" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A507" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="508" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A508" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="509" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A509" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="510" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A510" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="511" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A511" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="512" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A512" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="513" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A513" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="514" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A514" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="515" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A515" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="516" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A516" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="517" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A517" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="518" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A518" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="519" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A519" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="520" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A520" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="521" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A521" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="522" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A522" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="523" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A523" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="524" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A524" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="525" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A525" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="526" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A526" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="527" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A527" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="528" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A528" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="529" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A529" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="530" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A530" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="531" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A531" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="532" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A532" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="533" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A533" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="534" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A534" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="535" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A535" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="536" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A536" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="537" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A537" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="538" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A538" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="539" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A539" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="540" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A540" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="541" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A541" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="542" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A542" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="543" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A543" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="544" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A544" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="545" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A545" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="546" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A546" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="547" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A547" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="548" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A548" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="549" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A549" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="550" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A550" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="551" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A551" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="552" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A552" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="553" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A553" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="554" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A554" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="555" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A555" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="556" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A556" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="557" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A557" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="558" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A558" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="559" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A559" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="560" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A560" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="561" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A561" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="562" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A562" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="563" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A563" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="564" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A564" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="565" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A565" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="566" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A566" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="567" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A567" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="568" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A568" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="569" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A569" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="570" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A570" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="571" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A571" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="572" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A572" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="573" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A573" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="574" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A574" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="575" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A575" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="576" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A576" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="577" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A577" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="578" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A578" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="579" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A579" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="580" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A580" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="581" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A581" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="582" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A582" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="583" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A583" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="584" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A584" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="585" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A585" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="586" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A586" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="587" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A587" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="588" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A588" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="589" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A589" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="590" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A590" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="591" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A591" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="592" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A592" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="593" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A593" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="594" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A594" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="595" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A595" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="596" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A596" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="597" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A597" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="598" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A598" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="599" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A599" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="600" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A600" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="601" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A601" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="602" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A602" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="603" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A603" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="604" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A604" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="605" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A605" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="606" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A606" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="607" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A607" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="608" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A608" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="609" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A609" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="610" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A610" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="611" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A611" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="612" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A612" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="613" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A613" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="614" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A614" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="615" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A615" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="616" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A616" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="617" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A617" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="618" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A618" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="619" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A619" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="620" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A620" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="621" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A621" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="622" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A622" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="623" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A623" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="624" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A624" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="625" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A625" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="626" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A626" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="627" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A627" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="628" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A628" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="629" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A629" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="630" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A630" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="631" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A631" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="632" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A632" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="633" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A633" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="634" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A634" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="635" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A635" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="636" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A636" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="637" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A637" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="638" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A638" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="639" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A639" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="640" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A640" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="641" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A641" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="642" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A642" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="643" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A643" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="644" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A644" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="645" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A645" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="646" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A646" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="647" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A647" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="648" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A648" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="649" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A649" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="650" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A650" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="651" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A651" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
     </row>
     <row r="652" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A652" s="1" t="str">
-        <f t="shared" ref="A652:A698" si="6">IF(B651&lt;&gt;"", A651+1, "")</f>
+        <f t="shared" ref="A652:A698" si="7">IF(B651&lt;&gt;"", A651+1, "")</f>
         <v/>
       </c>
     </row>
     <row r="653" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A653" s="1" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="654" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A654" s="1" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="655" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A655" s="1" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="656" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A656" s="1" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="657" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A657" s="1" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="658" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A658" s="1" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="659" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A659" s="1" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="660" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A660" s="1" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="661" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A661" s="1" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="662" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A662" s="1" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="663" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A663" s="1" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="664" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A664" s="1" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="665" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A665" s="1" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="666" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A666" s="1" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="667" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A667" s="1" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="668" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A668" s="1" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="669" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A669" s="1" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="670" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A670" s="1" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="671" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A671" s="1" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="672" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A672" s="1" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="673" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A673" s="1" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="674" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A674" s="1" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="675" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A675" s="1" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="676" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A676" s="1" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="677" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A677" s="1" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="678" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A678" s="1" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="679" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A679" s="1" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="680" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A680" s="1" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="681" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A681" s="1" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="682" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A682" s="1" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="683" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A683" s="1" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="684" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A684" s="1" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="685" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A685" s="1" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="686" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A686" s="1" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="687" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A687" s="1" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="688" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A688" s="1" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="689" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A689" s="1" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="690" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A690" s="1" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="691" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A691" s="1" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="692" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A692" s="1" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="693" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A693" s="1" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="694" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A694" s="1" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="695" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A695" s="1" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="696" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A696" s="1" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="697" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A697" s="1" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="698" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A698" s="1" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
@@ -8378,11 +8444,11 @@
         <v>4</v>
       </c>
       <c r="C2" s="1">
-        <v>3900</v>
+        <v>4000</v>
       </c>
       <c r="D2" s="1">
         <f t="shared" ref="D2:D82" si="0">IF(C2&lt;&gt;"", CEILING(C2* 1.4, 100), "")</f>
-        <v>5500</v>
+        <v>5600</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -8410,11 +8476,11 @@
         <v>10</v>
       </c>
       <c r="C4" s="1">
-        <v>1450</v>
+        <v>1600</v>
       </c>
       <c r="D4" s="1">
         <f t="shared" si="0"/>
-        <v>2100</v>
+        <v>2300</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -8442,11 +8508,11 @@
         <v>18</v>
       </c>
       <c r="C6" s="1">
-        <v>2550</v>
+        <v>2650</v>
       </c>
       <c r="D6" s="1">
         <f t="shared" si="0"/>
-        <v>3600</v>
+        <v>3800</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -8474,11 +8540,11 @@
         <v>28</v>
       </c>
       <c r="C8" s="1">
-        <v>3500</v>
+        <v>3900</v>
       </c>
       <c r="D8" s="1">
         <f t="shared" si="0"/>
-        <v>4900</v>
+        <v>5500</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -8490,11 +8556,11 @@
         <v>33</v>
       </c>
       <c r="C9" s="1">
-        <v>2800</v>
+        <v>3200</v>
       </c>
       <c r="D9" s="1">
         <f t="shared" si="0"/>
-        <v>4000</v>
+        <v>4500</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -8506,11 +8572,11 @@
         <v>37</v>
       </c>
       <c r="C10" s="1">
-        <v>1400</v>
+        <v>1550</v>
       </c>
       <c r="D10" s="1">
         <f t="shared" si="0"/>
-        <v>2000</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -8554,11 +8620,11 @@
         <v>49</v>
       </c>
       <c r="C13" s="1">
-        <v>2250</v>
+        <v>2500</v>
       </c>
       <c r="D13" s="1">
         <f t="shared" si="0"/>
-        <v>3200</v>
+        <v>3500</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -8570,11 +8636,11 @@
         <v>53</v>
       </c>
       <c r="C14" s="1">
-        <v>2500</v>
+        <v>2600</v>
       </c>
       <c r="D14" s="1">
         <f t="shared" si="0"/>
-        <v>3500</v>
+        <v>3700</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -8586,11 +8652,11 @@
         <v>55</v>
       </c>
       <c r="C15" s="1">
-        <v>2850</v>
+        <v>2950</v>
       </c>
       <c r="D15" s="1">
         <f t="shared" si="0"/>
-        <v>4000</v>
+        <v>4200</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -8618,11 +8684,11 @@
         <v>60</v>
       </c>
       <c r="C17" s="1">
-        <v>2250</v>
+        <v>2500</v>
       </c>
       <c r="D17" s="1">
         <f t="shared" si="0"/>
-        <v>3200</v>
+        <v>3500</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -8711,11 +8777,11 @@
         <v>76</v>
       </c>
       <c r="C23" s="1">
-        <v>1250</v>
+        <v>1400</v>
       </c>
       <c r="D23" s="1">
         <f t="shared" si="0"/>
-        <v>1800</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -8724,7 +8790,7 @@
         <v>162</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C24" s="1">
         <v>1250</v>
@@ -8740,7 +8806,7 @@
         <v>163</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C25" s="1">
         <v>2850</v>
@@ -8756,7 +8822,7 @@
         <v>164</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C26" s="1">
         <v>2500</v>
@@ -8772,7 +8838,7 @@
         <v>165</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C27" s="1">
         <v>2100</v>
@@ -8788,14 +8854,14 @@
         <v>166</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C28" s="1">
-        <v>1250</v>
+        <v>1400</v>
       </c>
       <c r="D28" s="1">
         <f t="shared" si="0"/>
-        <v>1800</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="29" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -8804,7 +8870,7 @@
         <v>167</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C29" s="1">
         <v>1250</v>
@@ -8820,14 +8886,14 @@
         <v>168</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C30" s="1">
-        <v>2100</v>
+        <v>2500</v>
       </c>
       <c r="D30" s="1">
         <f t="shared" si="0"/>
-        <v>3000</v>
+        <v>3500</v>
       </c>
     </row>
     <row r="31" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -8836,14 +8902,14 @@
         <v>169</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C31" s="1">
-        <v>2100</v>
+        <v>2500</v>
       </c>
       <c r="D31" s="1">
         <f t="shared" si="0"/>
-        <v>3000</v>
+        <v>3500</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -8852,7 +8918,7 @@
         <v>170</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D32" s="1" t="str">
         <f t="shared" si="0"/>
@@ -8865,7 +8931,7 @@
         <v>171</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C33" s="1">
         <v>2500</v>
@@ -8881,7 +8947,7 @@
         <v>172</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D34" s="1" t="str">
         <f t="shared" si="0"/>
@@ -8894,7 +8960,7 @@
         <v>173</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D35" s="1" t="str">
         <f t="shared" si="0"/>
@@ -8907,7 +8973,7 @@
         <v>174</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C36" s="1">
         <v>1250</v>
@@ -8923,7 +8989,7 @@
         <v>175</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C37" s="1">
         <v>1750</v>
@@ -8939,14 +9005,14 @@
         <v>176</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C38" s="1">
-        <v>1400</v>
+        <v>1500</v>
       </c>
       <c r="D38" s="1">
         <f t="shared" si="0"/>
-        <v>2000</v>
+        <v>2100</v>
       </c>
     </row>
     <row r="39" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -8955,7 +9021,7 @@
         <v>177</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C39" s="1">
         <v>1100</v>
@@ -8971,7 +9037,7 @@
         <v>178</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D40" s="1" t="str">
         <f t="shared" si="0"/>
@@ -8984,7 +9050,7 @@
         <v>179</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C41" s="1">
         <v>1750</v>
@@ -9000,7 +9066,7 @@
         <v>180</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C42" s="1">
         <v>1500</v>
@@ -9016,7 +9082,7 @@
         <v>181</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C43" s="1">
         <v>1100</v>
@@ -9032,7 +9098,7 @@
         <v>182</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D44" s="1" t="str">
         <f t="shared" si="0"/>
@@ -9045,7 +9111,7 @@
         <v>183</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C45" s="1">
         <v>1400</v>
@@ -9061,7 +9127,7 @@
         <v>184</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D46" s="1" t="str">
         <f t="shared" si="0"/>
@@ -9074,7 +9140,7 @@
         <v>185</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C47" s="1">
         <v>2100</v>
@@ -9090,7 +9156,7 @@
         <v>186</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D48" s="1" t="str">
         <f t="shared" si="0"/>
@@ -9103,7 +9169,7 @@
         <v>187</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D49" s="1" t="str">
         <f t="shared" si="0"/>
@@ -9116,7 +9182,7 @@
         <v>188</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C50" s="1">
         <v>1250</v>
@@ -9132,7 +9198,7 @@
         <v>189</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C51" s="1">
         <v>1750</v>
@@ -9148,7 +9214,7 @@
         <v>190</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C52" s="1">
         <v>1400</v>
@@ -9164,7 +9230,7 @@
         <v>191</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C53" s="1">
         <v>1150</v>
@@ -9180,7 +9246,7 @@
         <v>192</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D54" s="1" t="str">
         <f t="shared" si="0"/>
@@ -9193,7 +9259,7 @@
         <v>193</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C55" s="1">
         <v>900</v>
@@ -9209,7 +9275,7 @@
         <v>194</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C56" s="1">
         <v>1400</v>
@@ -9225,14 +9291,14 @@
         <v>195</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C57" s="1">
-        <v>2550</v>
+        <v>2750</v>
       </c>
       <c r="D57" s="1">
         <f t="shared" si="0"/>
-        <v>3600</v>
+        <v>3900</v>
       </c>
     </row>
     <row r="58" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -9241,7 +9307,7 @@
         <v>196</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C58" s="1">
         <v>1000</v>
@@ -9257,7 +9323,7 @@
         <v>197</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C59" s="1">
         <v>550</v>
@@ -9273,7 +9339,7 @@
         <v>198</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C60" s="1">
         <v>1000</v>
@@ -9289,14 +9355,14 @@
         <v>199</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C61" s="1">
-        <v>1200</v>
+        <v>1250</v>
       </c>
       <c r="D61" s="1">
         <f t="shared" si="0"/>
-        <v>1700</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="62" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -9305,7 +9371,7 @@
         <v>200</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="D62" s="1" t="str">
         <f t="shared" si="0"/>
@@ -9318,11 +9384,14 @@
         <v>201</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>236</v>
-      </c>
-      <c r="D63" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
+        <v>235</v>
+      </c>
+      <c r="C63">
+        <v>2100</v>
+      </c>
+      <c r="D63" s="1">
+        <f t="shared" si="0"/>
+        <v>3000</v>
       </c>
     </row>
     <row r="64" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -9331,7 +9400,7 @@
         <v>202</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="D64" s="1" t="str">
         <f t="shared" si="0"/>
@@ -9344,14 +9413,14 @@
         <v>203</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C65" s="1">
-        <v>1950</v>
+        <v>2100</v>
       </c>
       <c r="D65" s="1">
         <f t="shared" si="0"/>
-        <v>2800</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="66" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -9360,7 +9429,7 @@
         <v>204</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="D66" s="1" t="str">
         <f t="shared" si="0"/>
@@ -9373,11 +9442,14 @@
         <v>205</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="D67" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
+        <v>242</v>
+      </c>
+      <c r="C67">
+        <v>2750</v>
+      </c>
+      <c r="D67" s="1">
+        <f t="shared" si="0"/>
+        <v>3900</v>
       </c>
     </row>
     <row r="68" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -9386,14 +9458,14 @@
         <v>206</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C68" s="1">
-        <v>2100</v>
+        <v>2500</v>
       </c>
       <c r="D68" s="1">
         <f t="shared" si="0"/>
-        <v>3000</v>
+        <v>3500</v>
       </c>
     </row>
     <row r="69" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -9402,7 +9474,7 @@
         <v>207</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="D69" s="1" t="str">
         <f t="shared" si="0"/>
@@ -9415,14 +9487,14 @@
         <v>208</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C70" s="1">
-        <v>2100</v>
+        <v>2500</v>
       </c>
       <c r="D70" s="1">
         <f t="shared" si="0"/>
-        <v>3000</v>
+        <v>3500</v>
       </c>
     </row>
     <row r="71" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -9431,14 +9503,14 @@
         <v>209</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C71" s="1">
-        <v>1750</v>
+        <v>1950</v>
       </c>
       <c r="D71" s="1">
         <f t="shared" si="0"/>
-        <v>2500</v>
+        <v>2800</v>
       </c>
     </row>
     <row r="72" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -9447,7 +9519,7 @@
         <v>210</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C72" s="1">
         <v>550</v>
@@ -9463,7 +9535,7 @@
         <v>211</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C73" s="1">
         <v>550</v>
@@ -9479,7 +9551,7 @@
         <v>212</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C74" s="1">
         <v>400</v>
@@ -9495,7 +9567,7 @@
         <v>213</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="D75" s="1" t="str">
         <f t="shared" si="0"/>
@@ -9508,7 +9580,7 @@
         <v>214</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C76" s="1">
         <v>1750</v>
@@ -9524,7 +9596,7 @@
         <v>215</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D77" s="1" t="str">
         <f t="shared" si="0"/>
@@ -9537,7 +9609,7 @@
         <v>216</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C78" s="1">
         <v>1750</v>
@@ -9553,14 +9625,14 @@
         <v>217</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C79" s="1">
-        <v>2250</v>
+        <v>2350</v>
       </c>
       <c r="D79" s="1">
         <f t="shared" si="0"/>
-        <v>3200</v>
+        <v>3300</v>
       </c>
     </row>
     <row r="80" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -9569,7 +9641,7 @@
         <v>218</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C80" s="1">
         <v>1400</v>
@@ -9585,7 +9657,7 @@
         <v>219</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C81" s="1">
         <v>2500</v>
@@ -10559,11 +10631,11 @@
         <v>5</v>
       </c>
       <c r="C2" s="1">
-        <v>2700</v>
+        <v>2850</v>
       </c>
       <c r="D2" s="1">
         <f t="shared" ref="D2:D82" si="0">IF(C2&lt;&gt;"", CEILING(C2* 1.4, 100), "")</f>
-        <v>3800</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -10607,11 +10679,11 @@
         <v>24</v>
       </c>
       <c r="C5" s="1">
-        <v>2700</v>
+        <v>2850</v>
       </c>
       <c r="D5" s="1">
         <f t="shared" si="0"/>
-        <v>3800</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -10655,11 +10727,11 @@
         <v>43</v>
       </c>
       <c r="C8" s="1">
-        <v>2250</v>
+        <v>2400</v>
       </c>
       <c r="D8" s="1">
         <f t="shared" si="0"/>
-        <v>3200</v>
+        <v>3400</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -10687,11 +10759,11 @@
         <v>56</v>
       </c>
       <c r="C10" s="1">
-        <v>1400</v>
+        <v>1450</v>
       </c>
       <c r="D10" s="1">
         <f t="shared" si="0"/>
-        <v>2000</v>
+        <v>2100</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -10700,14 +10772,14 @@
         <v>229</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C11" s="1">
-        <v>2100</v>
+        <v>2250</v>
       </c>
       <c r="D11" s="1">
         <f t="shared" si="0"/>
-        <v>3000</v>
+        <v>3200</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -10716,14 +10788,14 @@
         <v>230</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C12" s="1">
-        <v>2000</v>
+        <v>2050</v>
       </c>
       <c r="D12" s="1">
         <f t="shared" si="0"/>
-        <v>2800</v>
+        <v>2900</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -10732,14 +10804,14 @@
         <v>231</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C13" s="1">
-        <v>1250</v>
+        <v>1300</v>
       </c>
       <c r="D13" s="1">
         <f t="shared" si="0"/>
-        <v>1800</v>
+        <v>1900</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -10748,14 +10820,14 @@
         <v>232</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C14" s="1">
-        <v>2700</v>
+        <v>3000</v>
       </c>
       <c r="D14" s="1">
         <f t="shared" si="0"/>
-        <v>3800</v>
+        <v>4200</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -10764,7 +10836,7 @@
         <v>233</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D15" s="1" t="str">
         <f t="shared" si="0"/>
@@ -10777,7 +10849,7 @@
         <v>234</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D16" s="1" t="str">
         <f t="shared" si="0"/>
@@ -10790,7 +10862,7 @@
         <v>235</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C17" s="1">
         <v>2000</v>
@@ -10806,7 +10878,7 @@
         <v>236</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C18" s="1">
         <v>3900</v>
@@ -10822,7 +10894,7 @@
         <v>237</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D19" s="1" t="str">
         <f t="shared" si="0"/>
@@ -10835,14 +10907,14 @@
         <v>238</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C20" s="1">
-        <v>2700</v>
+        <v>2850</v>
       </c>
       <c r="D20" s="1">
         <f t="shared" si="0"/>
-        <v>3800</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -10851,7 +10923,7 @@
         <v>239</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D21" s="1" t="str">
         <f t="shared" si="0"/>
@@ -10864,11 +10936,14 @@
         <v>240</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="D22" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
+        <v>157</v>
+      </c>
+      <c r="C22">
+        <v>1750</v>
+      </c>
+      <c r="D22" s="1">
+        <f t="shared" si="0"/>
+        <v>2500</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -10877,7 +10952,7 @@
         <v>241</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C23" s="1">
         <v>4050</v>
@@ -10893,7 +10968,7 @@
         <v>242</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C24" s="1">
         <v>3200</v>
@@ -10909,7 +10984,7 @@
         <v>243</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C25" s="1">
         <v>1750</v>
@@ -10925,14 +11000,14 @@
         <v>244</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C26" s="1">
-        <v>4150</v>
+        <v>4600</v>
       </c>
       <c r="D26" s="1">
         <f t="shared" si="0"/>
-        <v>5900</v>
+        <v>6500</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -10941,14 +11016,14 @@
         <v>245</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C27" s="1">
-        <v>3900</v>
+        <v>4450</v>
       </c>
       <c r="D27" s="1">
         <f t="shared" si="0"/>
-        <v>5500</v>
+        <v>6300</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -10957,7 +11032,7 @@
         <v>246</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C28" s="1">
         <v>3200</v>
@@ -10973,14 +11048,14 @@
         <v>247</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C29" s="1">
-        <v>3000</v>
+        <v>3050</v>
       </c>
       <c r="D29" s="1">
         <f t="shared" si="0"/>
-        <v>4200</v>
+        <v>4300</v>
       </c>
     </row>
     <row r="30" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -10989,7 +11064,7 @@
         <v>248</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C30" s="1">
         <v>2500</v>
@@ -11005,7 +11080,7 @@
         <v>249</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C31" s="1">
         <v>2800</v>
@@ -11021,7 +11096,7 @@
         <v>250</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C32" s="1">
         <v>2250</v>
@@ -11037,7 +11112,7 @@
         <v>251</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C33" s="1">
         <v>1750</v>
@@ -11053,11 +11128,14 @@
         <v>252</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="D34" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
+        <v>216</v>
+      </c>
+      <c r="C34" s="3">
+        <v>2500</v>
+      </c>
+      <c r="D34" s="1">
+        <f t="shared" si="0"/>
+        <v>3500</v>
       </c>
     </row>
     <row r="35" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -11066,7 +11144,7 @@
         <v>253</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C35" s="1">
         <v>2100</v>
@@ -11082,7 +11160,7 @@
         <v>254</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C36" s="1">
         <v>1750</v>
@@ -11098,7 +11176,7 @@
         <v>255</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C37" s="1">
         <v>1550</v>
@@ -11114,7 +11192,7 @@
         <v>256</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C38" s="1">
         <v>1400</v>
@@ -11130,7 +11208,7 @@
         <v>257</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C39" s="1">
         <v>1250</v>
@@ -11146,7 +11224,7 @@
         <v>258</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C40" s="1">
         <v>1100</v>
@@ -11162,14 +11240,14 @@
         <v>259</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C41" s="1">
-        <v>15000</v>
+        <v>15650</v>
       </c>
       <c r="D41" s="1">
         <f t="shared" si="0"/>
-        <v>21000</v>
+        <v>22000</v>
       </c>
     </row>
     <row r="42" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -11178,7 +11256,7 @@
         <v>260</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C42" s="1">
         <v>10000</v>
@@ -11194,7 +11272,7 @@
         <v>261</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C43" s="1">
         <v>6750</v>
@@ -11210,7 +11288,7 @@
         <v>262</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C44" s="1">
         <v>3900</v>
@@ -11226,7 +11304,7 @@
         <v>263</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D45" s="1" t="str">
         <f t="shared" si="0"/>
@@ -11239,7 +11317,7 @@
         <v>264</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D46" s="1" t="str">
         <f t="shared" si="0"/>
@@ -11252,7 +11330,7 @@
         <v>265</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C47" s="1">
         <v>3500</v>
@@ -11268,7 +11346,7 @@
         <v>266</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C48" s="1">
         <v>1200</v>
@@ -11284,7 +11362,7 @@
         <v>267</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C49" s="1">
         <v>800</v>
@@ -11300,7 +11378,7 @@
         <v>268</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C50" s="1">
         <v>1050</v>
@@ -11316,7 +11394,7 @@
         <v>269</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C51" s="1">
         <v>800</v>
@@ -11332,7 +11410,7 @@
         <v>270</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C52" s="1">
         <v>7750</v>
@@ -11348,7 +11426,7 @@
         <v>271</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C53" s="1">
         <v>4600</v>
@@ -11364,7 +11442,7 @@
         <v>272</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C54" s="1">
         <v>3900</v>
@@ -12613,7 +12691,7 @@
     </row>
     <row r="3" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
-        <f t="shared" ref="A3:A59" si="1">IF(B2&lt;&gt;"", A2+1, "")</f>
+        <f t="shared" ref="A3:A66" si="1">IF(B2&lt;&gt;"", A2+1, "")</f>
         <v>274</v>
       </c>
       <c r="B3" s="1" t="s">
@@ -12732,11 +12810,11 @@
         <v>34</v>
       </c>
       <c r="C10" s="1">
-        <v>2500</v>
+        <v>2700</v>
       </c>
       <c r="D10" s="1">
         <f t="shared" si="0"/>
-        <v>3500</v>
+        <v>3800</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -12748,27 +12826,27 @@
         <v>38</v>
       </c>
       <c r="C11" s="1">
-        <v>2100</v>
+        <v>2250</v>
       </c>
       <c r="D11" s="1">
         <f t="shared" si="0"/>
-        <v>3000</v>
+        <v>3200</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
-        <f t="shared" si="1"/>
+        <f>IF(B11&lt;&gt;"", A11+1, "")</f>
         <v>283</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>40</v>
       </c>
       <c r="C12" s="1">
-        <v>2100</v>
+        <v>2250</v>
       </c>
       <c r="D12" s="1">
         <f t="shared" si="0"/>
-        <v>3000</v>
+        <v>3200</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -12828,11 +12906,11 @@
         <v>54</v>
       </c>
       <c r="C16" s="1">
-        <v>1100</v>
+        <v>1200</v>
       </c>
       <c r="D16" s="1">
         <f t="shared" si="0"/>
-        <v>1600</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -12844,11 +12922,11 @@
         <v>57</v>
       </c>
       <c r="C17" s="1">
-        <v>1100</v>
+        <v>1200</v>
       </c>
       <c r="D17" s="1">
         <f t="shared" si="0"/>
-        <v>1600</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -12969,14 +13047,14 @@
         <v>296</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C25" s="1">
-        <v>1250</v>
+        <v>1350</v>
       </c>
       <c r="D25" s="1">
         <f t="shared" si="0"/>
-        <v>1800</v>
+        <v>1900</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -12985,14 +13063,14 @@
         <v>297</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C26" s="1">
-        <v>1000</v>
+        <v>1050</v>
       </c>
       <c r="D26" s="1">
         <f t="shared" si="0"/>
-        <v>1400</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -13001,7 +13079,7 @@
         <v>298</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C27" s="1">
         <v>1100</v>
@@ -13017,7 +13095,7 @@
         <v>299</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C28" s="1">
         <v>1100</v>
@@ -13033,7 +13111,7 @@
         <v>300</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C29" s="1">
         <v>1100</v>
@@ -13049,14 +13127,14 @@
         <v>301</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C30" s="1">
-        <v>1400</v>
+        <v>1550</v>
       </c>
       <c r="D30" s="1">
         <f t="shared" si="0"/>
-        <v>2000</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="31" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -13065,7 +13143,7 @@
         <v>302</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C31" s="1">
         <v>2000</v>
@@ -13081,7 +13159,7 @@
         <v>303</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C32" s="1">
         <v>700</v>
@@ -13097,7 +13175,7 @@
         <v>304</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C33" s="1">
         <v>1400</v>
@@ -13113,7 +13191,7 @@
         <v>305</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C34" s="1">
         <v>400</v>
@@ -13129,7 +13207,7 @@
         <v>306</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C35" s="1">
         <v>550</v>
@@ -13145,14 +13223,14 @@
         <v>307</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C36" s="1">
-        <v>300</v>
+        <v>380</v>
       </c>
       <c r="D36" s="1">
         <f t="shared" si="0"/>
-        <v>500</v>
+        <v>600</v>
       </c>
     </row>
     <row r="37" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -13161,7 +13239,7 @@
         <v>308</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C37" s="1">
         <v>700</v>
@@ -13177,7 +13255,7 @@
         <v>309</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C38" s="1">
         <v>1300</v>
@@ -13193,7 +13271,7 @@
         <v>310</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C39" s="1">
         <v>1400</v>
@@ -13209,14 +13287,14 @@
         <v>311</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C40" s="1">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="D40" s="1">
         <f t="shared" si="0"/>
-        <v>400</v>
+        <v>500</v>
       </c>
     </row>
     <row r="41" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -13225,7 +13303,7 @@
         <v>312</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C41" s="1">
         <v>1050</v>
@@ -13241,7 +13319,7 @@
         <v>313</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C42" s="1">
         <v>500</v>
@@ -13257,7 +13335,7 @@
         <v>314</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C43" s="1">
         <v>1750</v>
@@ -13273,7 +13351,7 @@
         <v>315</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C44" s="1">
         <v>1050</v>
@@ -13289,7 +13367,7 @@
         <v>316</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C45" s="1">
         <v>3150</v>
@@ -13305,14 +13383,14 @@
         <v>317</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C46" s="1">
-        <v>3500</v>
+        <v>3900</v>
       </c>
       <c r="D46" s="1">
         <f t="shared" si="0"/>
-        <v>4900</v>
+        <v>5500</v>
       </c>
     </row>
     <row r="47" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -13321,7 +13399,7 @@
         <v>318</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C47" s="1">
         <v>800</v>
@@ -13337,7 +13415,7 @@
         <v>319</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C48" s="1">
         <v>800</v>
@@ -13353,7 +13431,7 @@
         <v>320</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C49" s="1">
         <v>400</v>
@@ -13369,7 +13447,7 @@
         <v>321</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C50" s="1">
         <v>550</v>
@@ -13385,7 +13463,7 @@
         <v>322</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C51" s="1">
         <v>200</v>
@@ -13401,7 +13479,7 @@
         <v>323</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C52" s="1">
         <v>100</v>
@@ -13417,7 +13495,7 @@
         <v>324</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D53" s="1">
         <v>50</v>
@@ -13429,7 +13507,7 @@
         <v>325</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C54" s="1">
         <v>50</v>
@@ -13445,7 +13523,7 @@
         <v>326</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C55" s="1">
         <v>50</v>
@@ -13461,7 +13539,7 @@
         <v>327</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D56" s="1">
         <v>50</v>
@@ -13473,13 +13551,13 @@
         <v>328</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C57" s="1">
         <v>250</v>
       </c>
       <c r="D57" s="1">
-        <f t="shared" ref="D57:D59" si="3">IF(C57&lt;&gt;"", CEILING(C57 * 1.4, 100), "")</f>
+        <f t="shared" ref="D57:D62" si="3">IF(C57&lt;&gt;"", CEILING(C57 * 1.4, 100), "")</f>
         <v>400</v>
       </c>
     </row>
@@ -13489,7 +13567,7 @@
         <v>329</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C58" s="1">
         <v>100</v>
@@ -13505,7 +13583,7 @@
         <v>330</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C59" s="1">
         <v>250</v>
@@ -13515,27 +13593,102 @@
         <v>400</v>
       </c>
     </row>
-    <row r="60" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="61" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="62" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="63" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="64" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="65" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="66" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="67" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="68" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="69" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="70" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="71" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="72" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="73" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="74" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="75" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="76" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="77" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="78" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="79" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="80" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="60" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A60" s="1">
+        <f t="shared" si="1"/>
+        <v>331</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>432</v>
+      </c>
+      <c r="C60" s="3">
+        <v>2250</v>
+      </c>
+      <c r="D60" s="3">
+        <f t="shared" si="3"/>
+        <v>3200</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A61" s="1">
+        <f t="shared" si="1"/>
+        <v>332</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>433</v>
+      </c>
+      <c r="C61" s="3">
+        <v>1050</v>
+      </c>
+      <c r="D61" s="3">
+        <f t="shared" si="3"/>
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A62" s="1">
+        <f t="shared" si="1"/>
+        <v>333</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>434</v>
+      </c>
+      <c r="C62" s="3">
+        <v>550</v>
+      </c>
+      <c r="D62" s="3">
+        <f t="shared" si="3"/>
+        <v>800</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A63" s="1">
+        <f t="shared" si="1"/>
+        <v>334</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A64" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="65" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A65" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="66" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A66" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="67" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A67" s="1" t="str">
+        <f t="shared" ref="A67:A68" si="4">IF(B66&lt;&gt;"", A66+1, "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="68" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A68" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="69" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="70" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="71" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="72" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="73" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="74" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="75" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="76" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="77" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="78" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="79" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="80" spans="1:1" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="81" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="82" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="83" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -14493,7 +14646,7 @@
         <v>331</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C2" s="1">
         <v>550</v>
@@ -14509,7 +14662,7 @@
         <v>332</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C3" s="1">
         <v>1100</v>
@@ -14525,7 +14678,7 @@
         <v>333</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C4" s="1">
         <v>850</v>
@@ -14541,7 +14694,7 @@
         <v>334</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C5" s="1">
         <v>1400</v>
@@ -14557,7 +14710,7 @@
         <v>335</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C6" s="1">
         <v>600</v>
@@ -14573,7 +14726,7 @@
         <v>336</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C7" s="1">
         <v>900</v>
@@ -14589,7 +14742,7 @@
         <v>337</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C8" s="1">
         <v>1550</v>
@@ -14605,7 +14758,7 @@
         <v>338</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="C9" s="1">
         <v>3550</v>
@@ -14621,7 +14774,7 @@
         <v>339</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C10" s="1">
         <v>1400</v>
@@ -14637,7 +14790,7 @@
         <v>340</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C11" s="1">
         <v>1250</v>
@@ -14653,7 +14806,7 @@
         <v>341</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="C12" s="1">
         <v>1400</v>
@@ -14669,7 +14822,7 @@
         <v>342</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C13" s="1">
         <v>1150</v>
@@ -14685,7 +14838,7 @@
         <v>343</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="C14" s="1">
         <v>1750</v>
@@ -14701,7 +14854,7 @@
         <v>344</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C15" s="1">
         <v>1750</v>
@@ -14717,7 +14870,7 @@
         <v>345</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C16" s="1">
         <v>1050</v>
@@ -14733,7 +14886,7 @@
         <v>346</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C17" s="1">
         <v>2800</v>
@@ -14749,7 +14902,7 @@
         <v>347</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C18" s="1">
         <v>2500</v>
@@ -14765,7 +14918,7 @@
         <v>348</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C19" s="1">
         <v>3150</v>
@@ -14781,7 +14934,7 @@
         <v>349</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C20" s="1">
         <v>4250</v>
@@ -14797,7 +14950,7 @@
         <v>350</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C21" s="1">
         <v>1200</v>
@@ -14813,7 +14966,7 @@
         <v>351</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C22" s="1">
         <v>1050</v>
@@ -14829,7 +14982,7 @@
         <v>352</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C23" s="1">
         <v>1050</v>
@@ -14845,7 +14998,7 @@
         <v>353</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C24" s="1">
         <v>600</v>
@@ -14861,7 +15014,7 @@
         <v>354</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C25" s="1">
         <v>1050</v>
@@ -14877,7 +15030,7 @@
         <v>355</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C26" s="1">
         <v>5300</v>
@@ -14893,14 +15046,14 @@
         <v>356</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C27" s="1">
-        <v>4250</v>
+        <v>4600</v>
       </c>
       <c r="D27" s="1">
         <f t="shared" si="0"/>
-        <v>6000</v>
+        <v>6500</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -14909,14 +15062,14 @@
         <v>357</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C28" s="1">
-        <v>2150</v>
+        <v>2100</v>
       </c>
       <c r="D28" s="1">
         <f t="shared" si="0"/>
-        <v>3100</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="29" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -14925,7 +15078,7 @@
         <v>358</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C29" s="1">
         <v>1700</v>
@@ -14941,7 +15094,7 @@
         <v>359</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C30" s="1">
         <v>2750</v>
@@ -14957,7 +15110,7 @@
         <v>360</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C31" s="1">
         <v>3500</v>
@@ -14973,7 +15126,7 @@
         <v>361</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C32" s="1">
         <v>230</v>
@@ -14988,7 +15141,7 @@
         <v>362</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C33" s="1">
         <v>3200</v>
@@ -15004,7 +15157,7 @@
         <v>363</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C34" s="1">
         <v>1900</v>
@@ -15020,7 +15173,7 @@
         <v>364</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C35" s="1">
         <v>2100</v>
@@ -15036,7 +15189,7 @@
         <v>365</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C36" s="1">
         <v>1750</v>
@@ -15052,14 +15205,14 @@
         <v>366</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C37" s="1">
-        <v>2000</v>
+        <v>2100</v>
       </c>
       <c r="D37" s="1">
         <f t="shared" si="2"/>
-        <v>2800</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="38" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -15068,14 +15221,14 @@
         <v>367</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C38" s="1">
-        <v>2000</v>
+        <v>2450</v>
       </c>
       <c r="D38" s="1">
         <f t="shared" si="2"/>
-        <v>2800</v>
+        <v>3500</v>
       </c>
     </row>
     <row r="39" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -15084,7 +15237,7 @@
         <v>368</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C39" s="1">
         <v>3200</v>
@@ -15100,7 +15253,7 @@
         <v>369</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C40" s="1">
         <v>3200</v>
@@ -15116,7 +15269,7 @@
         <v>370</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C41" s="1">
         <v>2800</v>
@@ -15132,7 +15285,7 @@
         <v>371</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C42" s="1">
         <v>1050</v>
@@ -15148,7 +15301,7 @@
         <v>372</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C43" s="1">
         <v>1050</v>
@@ -15164,7 +15317,7 @@
         <v>373</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C44" s="1">
         <v>300</v>
@@ -15180,7 +15333,7 @@
         <v>374</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C45" s="1">
         <v>230</v>
@@ -15196,7 +15349,7 @@
         <v>375</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C46" s="1">
         <v>2100</v>
@@ -15212,7 +15365,7 @@
         <v>376</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C47" s="1">
         <v>2450</v>
@@ -15228,7 +15381,7 @@
         <v>377</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C48" s="1">
         <v>2550</v>
@@ -15244,7 +15397,7 @@
         <v>378</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C49" s="1">
         <v>2750</v>
@@ -15260,7 +15413,7 @@
         <v>379</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C50" s="1">
         <v>3200</v>
@@ -15276,7 +15429,7 @@
         <v>380</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C51" s="1">
         <v>1050</v>
@@ -15292,7 +15445,7 @@
         <v>381</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C52" s="1">
         <v>1050</v>
@@ -15308,7 +15461,7 @@
         <v>382</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C53" s="1">
         <v>1200</v>
@@ -15324,7 +15477,7 @@
         <v>383</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C54" s="1">
         <v>1050</v>
@@ -15340,7 +15493,7 @@
         <v>384</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C55" s="1">
         <v>1550</v>
@@ -15356,7 +15509,7 @@
         <v>385</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C56" s="1">
         <v>1200</v>
@@ -15372,7 +15525,7 @@
         <v>386</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C57" s="1">
         <v>2100</v>
@@ -15388,7 +15541,7 @@
         <v>387</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C58" s="1">
         <v>1100</v>
@@ -15404,7 +15557,7 @@
         <v>388</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C59" s="1">
         <v>2500</v>
@@ -15420,7 +15573,7 @@
         <v>389</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C60" s="1">
         <v>1400</v>
@@ -15436,7 +15589,7 @@
         <v>390</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C61" s="1">
         <v>1800</v>
@@ -15452,7 +15605,7 @@
         <v>391</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C62" s="1">
         <v>500</v>
@@ -15468,7 +15621,7 @@
         <v>392</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C63" s="1">
         <v>600</v>
@@ -15484,7 +15637,7 @@
         <v>393</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C64" s="1">
         <v>1250</v>
@@ -15500,7 +15653,7 @@
         <v>394</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C65" s="1">
         <v>1350</v>
@@ -15516,7 +15669,7 @@
         <v>395</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C66" s="1">
         <v>300</v>
@@ -15532,7 +15685,7 @@
         <v>396</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C67" s="1">
         <v>1600</v>
@@ -15548,7 +15701,7 @@
         <v>397</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C68" s="1">
         <v>550</v>
@@ -15564,7 +15717,7 @@
         <v>398</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C69" s="1">
         <v>1750</v>
@@ -15580,7 +15733,7 @@
         <v>399</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C70" s="1">
         <v>1050</v>
@@ -15596,7 +15749,7 @@
         <v>400</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C71" s="1">
         <v>1750</v>
@@ -15612,7 +15765,7 @@
         <v>401</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C72" s="1">
         <v>1050</v>
@@ -15628,7 +15781,7 @@
         <v>402</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C73" s="1">
         <v>1750</v>
@@ -15644,7 +15797,7 @@
         <v>403</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C74" s="1">
         <v>2100</v>
@@ -15660,7 +15813,7 @@
         <v>404</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C75" s="1">
         <v>200</v>
@@ -15676,7 +15829,7 @@
         <v>405</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C76" s="1">
         <v>600</v>
@@ -15692,7 +15845,7 @@
         <v>406</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C77" s="1">
         <v>600</v>
@@ -15708,7 +15861,7 @@
         <v>407</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C78" s="1">
         <v>2450</v>
@@ -15724,7 +15877,7 @@
         <v>408</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C79" s="1">
         <v>2100</v>
@@ -15740,7 +15893,7 @@
         <v>409</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C80" s="1">
         <v>2450</v>
@@ -15756,7 +15909,7 @@
         <v>410</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C81" s="1">
         <v>1750</v>
@@ -15772,7 +15925,7 @@
         <v>411</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C82" s="1">
         <v>2800</v>
@@ -15788,7 +15941,7 @@
         <v>412</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C83" s="1">
         <v>1750</v>
@@ -15804,7 +15957,7 @@
         <v>413</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="C84" s="1">
         <v>1750</v>
@@ -15820,7 +15973,7 @@
         <v>414</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C85" s="1">
         <v>2100</v>
@@ -15836,7 +15989,7 @@
         <v>415</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C86" s="1">
         <v>1050</v>
@@ -15852,7 +16005,7 @@
         <v>416</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C87" s="1">
         <v>50</v>
@@ -15868,7 +16021,7 @@
         <v>417</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C88" s="1">
         <v>130</v>
@@ -15884,7 +16037,7 @@
         <v>418</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="C89" s="1">
         <v>280</v>
@@ -15899,7 +16052,7 @@
         <v>419</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="C90" s="1">
         <v>280</v>
@@ -15915,7 +16068,7 @@
         <v>420</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="C91" s="1">
         <v>1750</v>
@@ -15931,7 +16084,7 @@
         <v>421</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C92" s="1">
         <v>1750</v>
@@ -15947,7 +16100,7 @@
         <v>422</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C93" s="1">
         <v>1400</v>
@@ -15963,7 +16116,7 @@
         <v>423</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="C94" s="1">
         <v>600</v>
@@ -15979,7 +16132,7 @@
         <v>424</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C95" s="1">
         <v>3550</v>
@@ -15995,7 +16148,7 @@
         <v>425</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="C96" s="1">
         <v>2800</v>
@@ -16011,7 +16164,7 @@
         <v>426</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="C97" s="1">
         <v>700</v>
@@ -16027,7 +16180,7 @@
         <v>427</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C98" s="1">
         <v>200</v>
@@ -16042,35 +16195,53 @@
         <f t="shared" si="1"/>
         <v>428</v>
       </c>
-      <c r="D99" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="B99" s="3" t="s">
+        <v>435</v>
+      </c>
+      <c r="C99" s="3">
+        <v>1100</v>
+      </c>
+      <c r="D99" s="1">
+        <f t="shared" si="3"/>
+        <v>1600</v>
       </c>
     </row>
     <row r="100" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A100" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="D100" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A100" s="1">
+        <f t="shared" si="1"/>
+        <v>429</v>
+      </c>
+      <c r="B100" s="3" t="s">
+        <v>436</v>
+      </c>
+      <c r="C100" s="3">
+        <v>1750</v>
+      </c>
+      <c r="D100" s="1">
+        <f t="shared" si="3"/>
+        <v>2500</v>
       </c>
     </row>
     <row r="101" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A101" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="D101" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A101" s="1">
+        <f t="shared" si="1"/>
+        <v>430</v>
+      </c>
+      <c r="B101" s="3" t="s">
+        <v>437</v>
+      </c>
+      <c r="C101" s="3">
+        <v>2700</v>
+      </c>
+      <c r="D101" s="1">
+        <f t="shared" si="3"/>
+        <v>3800</v>
       </c>
     </row>
     <row r="102" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A102" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v/>
+      <c r="A102" s="1">
+        <f t="shared" si="1"/>
+        <v>431</v>
       </c>
       <c r="D102" s="1" t="str">
         <f t="shared" si="3"/>

--- a/inventario.xlsx.xlsx
+++ b/inventario.xlsx.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2746fa196ce476c0/Desktop/kiosco el tio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="201" documentId="11_F0BF34C6AB674EABCA5660F4A3CFFCC672003DE8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B99619DB-0BD3-43BA-80C6-B8C1B7B89A34}"/>
+  <xr:revisionPtr revIDLastSave="202" documentId="11_F0BF34C6AB674EABCA5660F4A3CFFCC672003DE8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AD8F3835-8350-4C8F-B2E0-F6347557BA73}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="457" uniqueCount="443">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="457" uniqueCount="442">
   <si>
     <t>CODIGO</t>
   </si>
@@ -1357,9 +1357,6 @@
   </si>
   <si>
     <t>PAN HAMBURGUESA DON YEYO CHICO</t>
-  </si>
-  <si>
-    <t>I</t>
   </si>
   <si>
     <t>SIDIET 250CC</t>
@@ -1411,13 +1408,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1658,7 +1654,7 @@
         <v>6</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>440</v>
+        <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -2100,7 +2096,7 @@
       <c r="B29" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="C29" s="3">
+      <c r="C29">
         <v>4250</v>
       </c>
       <c r="D29" s="1">
@@ -2775,7 +2771,7 @@
       <c r="B72" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="C72" s="3">
+      <c r="C72">
         <v>1400</v>
       </c>
       <c r="D72" s="1">
@@ -3553,7 +3549,7 @@
       <c r="B121" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="C121" s="3">
+      <c r="C121">
         <v>1750</v>
       </c>
       <c r="D121" s="1">
@@ -3849,10 +3845,10 @@
         <f t="shared" ref="A141:A145" si="4">IF(B140&lt;&gt;"", A140+1, "")</f>
         <v>140</v>
       </c>
-      <c r="B141" s="3" t="s">
+      <c r="B141" t="s">
         <v>439</v>
       </c>
-      <c r="C141" s="3">
+      <c r="C141">
         <v>1750</v>
       </c>
       <c r="D141" s="1">
@@ -3865,10 +3861,10 @@
         <f t="shared" si="4"/>
         <v>141</v>
       </c>
-      <c r="B142" s="3" t="s">
-        <v>441</v>
-      </c>
-      <c r="C142" s="3">
+      <c r="B142" t="s">
+        <v>440</v>
+      </c>
+      <c r="C142">
         <v>1400</v>
       </c>
       <c r="D142" s="1">
@@ -3881,10 +3877,10 @@
         <f t="shared" si="4"/>
         <v>142</v>
       </c>
-      <c r="B143" s="3" t="s">
-        <v>442</v>
-      </c>
-      <c r="C143" s="3">
+      <c r="B143" t="s">
+        <v>441</v>
+      </c>
+      <c r="C143">
         <v>1550</v>
       </c>
       <c r="D143" s="1">
@@ -3914,7 +3910,7 @@
     </row>
     <row r="146" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A146" s="1" t="str">
-        <f t="shared" ref="A142:A396" si="5">IF(B145&lt;&gt;"", A145+1, "")</f>
+        <f t="shared" ref="A146:A396" si="5">IF(B145&lt;&gt;"", A145+1, "")</f>
         <v/>
       </c>
       <c r="D146" s="1" t="str">
@@ -11130,7 +11126,7 @@
       <c r="B34" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="C34" s="3">
+      <c r="C34">
         <v>2500</v>
       </c>
       <c r="D34" s="1">
@@ -13598,13 +13594,13 @@
         <f t="shared" si="1"/>
         <v>331</v>
       </c>
-      <c r="B60" s="3" t="s">
+      <c r="B60" t="s">
         <v>432</v>
       </c>
-      <c r="C60" s="3">
+      <c r="C60">
         <v>2250</v>
       </c>
-      <c r="D60" s="3">
+      <c r="D60">
         <f t="shared" si="3"/>
         <v>3200</v>
       </c>
@@ -13614,13 +13610,13 @@
         <f t="shared" si="1"/>
         <v>332</v>
       </c>
-      <c r="B61" s="3" t="s">
+      <c r="B61" t="s">
         <v>433</v>
       </c>
-      <c r="C61" s="3">
+      <c r="C61">
         <v>1050</v>
       </c>
-      <c r="D61" s="3">
+      <c r="D61">
         <f t="shared" si="3"/>
         <v>1500</v>
       </c>
@@ -13630,13 +13626,13 @@
         <f t="shared" si="1"/>
         <v>333</v>
       </c>
-      <c r="B62" s="3" t="s">
+      <c r="B62" t="s">
         <v>434</v>
       </c>
-      <c r="C62" s="3">
+      <c r="C62">
         <v>550</v>
       </c>
-      <c r="D62" s="3">
+      <c r="D62">
         <f t="shared" si="3"/>
         <v>800</v>
       </c>
@@ -16195,10 +16191,10 @@
         <f t="shared" si="1"/>
         <v>428</v>
       </c>
-      <c r="B99" s="3" t="s">
+      <c r="B99" t="s">
         <v>435</v>
       </c>
-      <c r="C99" s="3">
+      <c r="C99">
         <v>1100</v>
       </c>
       <c r="D99" s="1">
@@ -16211,10 +16207,10 @@
         <f t="shared" si="1"/>
         <v>429</v>
       </c>
-      <c r="B100" s="3" t="s">
+      <c r="B100" t="s">
         <v>436</v>
       </c>
-      <c r="C100" s="3">
+      <c r="C100">
         <v>1750</v>
       </c>
       <c r="D100" s="1">
@@ -16227,10 +16223,10 @@
         <f t="shared" si="1"/>
         <v>430</v>
       </c>
-      <c r="B101" s="3" t="s">
+      <c r="B101" t="s">
         <v>437</v>
       </c>
-      <c r="C101" s="3">
+      <c r="C101">
         <v>2700</v>
       </c>
       <c r="D101" s="1">

--- a/inventario.xlsx.xlsx
+++ b/inventario.xlsx.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2746fa196ce476c0/Desktop/kiosco el tio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="202" documentId="11_F0BF34C6AB674EABCA5660F4A3CFFCC672003DE8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AD8F3835-8350-4C8F-B2E0-F6347557BA73}"/>
+  <xr:revisionPtr revIDLastSave="204" documentId="11_F0BF34C6AB674EABCA5660F4A3CFFCC672003DE8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0F7CA3BE-0132-4877-95E1-F57AF83A4B42}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Comestibles" sheetId="1" r:id="rId1"/>
@@ -1071,9 +1071,6 @@
     <t>JABON LIQUIDO SUELTO X L</t>
   </si>
   <si>
-    <t xml:space="preserve">JABON LIQUIDO DRANDY </t>
-  </si>
-  <si>
     <t>SUABIZANTE SUELTO X L</t>
   </si>
   <si>
@@ -1363,6 +1360,9 @@
   </si>
   <si>
     <t>YERBA MAÑANITA 500G</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JABON LIQUIDO DRANBY </t>
   </si>
 </sst>
 </file>
@@ -1429,10 +1429,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1982,7 +1978,7 @@
         <v>21</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="C22" s="1">
         <v>1950</v>
@@ -3846,7 +3842,7 @@
         <v>140</v>
       </c>
       <c r="B141" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C141">
         <v>1750</v>
@@ -3862,7 +3858,7 @@
         <v>141</v>
       </c>
       <c r="B142" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C142">
         <v>1400</v>
@@ -3878,7 +3874,7 @@
         <v>142</v>
       </c>
       <c r="B143" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C143">
         <v>1550</v>
@@ -13595,7 +13591,7 @@
         <v>331</v>
       </c>
       <c r="B60" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C60">
         <v>2250</v>
@@ -13611,7 +13607,7 @@
         <v>332</v>
       </c>
       <c r="B61" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C61">
         <v>1050</v>
@@ -13627,7 +13623,7 @@
         <v>333</v>
       </c>
       <c r="B62" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C62">
         <v>550</v>
@@ -14786,14 +14782,14 @@
         <v>340</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>344</v>
+        <v>441</v>
       </c>
       <c r="C11" s="1">
-        <v>1250</v>
+        <v>2000</v>
       </c>
       <c r="D11" s="1">
         <f t="shared" si="0"/>
-        <v>1800</v>
+        <v>2800</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -14802,7 +14798,7 @@
         <v>341</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C12" s="1">
         <v>1400</v>
@@ -14818,7 +14814,7 @@
         <v>342</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="C13" s="1">
         <v>1150</v>
@@ -14834,7 +14830,7 @@
         <v>343</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C14" s="1">
         <v>1750</v>
@@ -14850,7 +14846,7 @@
         <v>344</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="C15" s="1">
         <v>1750</v>
@@ -14866,7 +14862,7 @@
         <v>345</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C16" s="1">
         <v>1050</v>
@@ -14882,7 +14878,7 @@
         <v>346</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C17" s="1">
         <v>2800</v>
@@ -14898,7 +14894,7 @@
         <v>347</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C18" s="1">
         <v>2500</v>
@@ -14914,7 +14910,7 @@
         <v>348</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C19" s="1">
         <v>3150</v>
@@ -14930,7 +14926,7 @@
         <v>349</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C20" s="1">
         <v>4250</v>
@@ -14946,7 +14942,7 @@
         <v>350</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C21" s="1">
         <v>1200</v>
@@ -14962,7 +14958,7 @@
         <v>351</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C22" s="1">
         <v>1050</v>
@@ -14978,7 +14974,7 @@
         <v>352</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C23" s="1">
         <v>1050</v>
@@ -14994,7 +14990,7 @@
         <v>353</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C24" s="1">
         <v>600</v>
@@ -15010,7 +15006,7 @@
         <v>354</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C25" s="1">
         <v>1050</v>
@@ -15026,7 +15022,7 @@
         <v>355</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C26" s="1">
         <v>5300</v>
@@ -15042,7 +15038,7 @@
         <v>356</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C27" s="1">
         <v>4600</v>
@@ -15058,7 +15054,7 @@
         <v>357</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C28" s="1">
         <v>2100</v>
@@ -15074,7 +15070,7 @@
         <v>358</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C29" s="1">
         <v>1700</v>
@@ -15090,7 +15086,7 @@
         <v>359</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C30" s="1">
         <v>2750</v>
@@ -15106,7 +15102,7 @@
         <v>360</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C31" s="1">
         <v>3500</v>
@@ -15122,7 +15118,7 @@
         <v>361</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C32" s="1">
         <v>230</v>
@@ -15137,7 +15133,7 @@
         <v>362</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C33" s="1">
         <v>3200</v>
@@ -15153,7 +15149,7 @@
         <v>363</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C34" s="1">
         <v>1900</v>
@@ -15169,7 +15165,7 @@
         <v>364</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C35" s="1">
         <v>2100</v>
@@ -15185,7 +15181,7 @@
         <v>365</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C36" s="1">
         <v>1750</v>
@@ -15201,7 +15197,7 @@
         <v>366</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C37" s="1">
         <v>2100</v>
@@ -15217,7 +15213,7 @@
         <v>367</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C38" s="1">
         <v>2450</v>
@@ -15233,7 +15229,7 @@
         <v>368</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C39" s="1">
         <v>3200</v>
@@ -15249,7 +15245,7 @@
         <v>369</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C40" s="1">
         <v>3200</v>
@@ -15265,7 +15261,7 @@
         <v>370</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C41" s="1">
         <v>2800</v>
@@ -15281,7 +15277,7 @@
         <v>371</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C42" s="1">
         <v>1050</v>
@@ -15297,7 +15293,7 @@
         <v>372</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C43" s="1">
         <v>1050</v>
@@ -15313,7 +15309,7 @@
         <v>373</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C44" s="1">
         <v>300</v>
@@ -15329,7 +15325,7 @@
         <v>374</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C45" s="1">
         <v>230</v>
@@ -15345,7 +15341,7 @@
         <v>375</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C46" s="1">
         <v>2100</v>
@@ -15361,7 +15357,7 @@
         <v>376</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C47" s="1">
         <v>2450</v>
@@ -15377,7 +15373,7 @@
         <v>377</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C48" s="1">
         <v>2550</v>
@@ -15393,7 +15389,7 @@
         <v>378</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C49" s="1">
         <v>2750</v>
@@ -15409,7 +15405,7 @@
         <v>379</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C50" s="1">
         <v>3200</v>
@@ -15425,7 +15421,7 @@
         <v>380</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C51" s="1">
         <v>1050</v>
@@ -15441,7 +15437,7 @@
         <v>381</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C52" s="1">
         <v>1050</v>
@@ -15457,7 +15453,7 @@
         <v>382</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C53" s="1">
         <v>1200</v>
@@ -15473,7 +15469,7 @@
         <v>383</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C54" s="1">
         <v>1050</v>
@@ -15489,7 +15485,7 @@
         <v>384</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C55" s="1">
         <v>1550</v>
@@ -15505,7 +15501,7 @@
         <v>385</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C56" s="1">
         <v>1200</v>
@@ -15521,7 +15517,7 @@
         <v>386</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C57" s="1">
         <v>2100</v>
@@ -15537,7 +15533,7 @@
         <v>387</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C58" s="1">
         <v>1100</v>
@@ -15553,7 +15549,7 @@
         <v>388</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C59" s="1">
         <v>2500</v>
@@ -15569,7 +15565,7 @@
         <v>389</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C60" s="1">
         <v>1400</v>
@@ -15585,7 +15581,7 @@
         <v>390</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C61" s="1">
         <v>1800</v>
@@ -15601,7 +15597,7 @@
         <v>391</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C62" s="1">
         <v>500</v>
@@ -15617,7 +15613,7 @@
         <v>392</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C63" s="1">
         <v>600</v>
@@ -15633,7 +15629,7 @@
         <v>393</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C64" s="1">
         <v>1250</v>
@@ -15649,7 +15645,7 @@
         <v>394</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C65" s="1">
         <v>1350</v>
@@ -15665,7 +15661,7 @@
         <v>395</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C66" s="1">
         <v>300</v>
@@ -15681,7 +15677,7 @@
         <v>396</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C67" s="1">
         <v>1600</v>
@@ -15697,7 +15693,7 @@
         <v>397</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C68" s="1">
         <v>550</v>
@@ -15713,7 +15709,7 @@
         <v>398</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C69" s="1">
         <v>1750</v>
@@ -15729,7 +15725,7 @@
         <v>399</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C70" s="1">
         <v>1050</v>
@@ -15745,7 +15741,7 @@
         <v>400</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C71" s="1">
         <v>1750</v>
@@ -15761,7 +15757,7 @@
         <v>401</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C72" s="1">
         <v>1050</v>
@@ -15777,7 +15773,7 @@
         <v>402</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C73" s="1">
         <v>1750</v>
@@ -15793,7 +15789,7 @@
         <v>403</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C74" s="1">
         <v>2100</v>
@@ -15809,7 +15805,7 @@
         <v>404</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C75" s="1">
         <v>200</v>
@@ -15825,7 +15821,7 @@
         <v>405</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C76" s="1">
         <v>600</v>
@@ -15841,7 +15837,7 @@
         <v>406</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C77" s="1">
         <v>600</v>
@@ -15857,7 +15853,7 @@
         <v>407</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C78" s="1">
         <v>2450</v>
@@ -15873,7 +15869,7 @@
         <v>408</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C79" s="1">
         <v>2100</v>
@@ -15889,7 +15885,7 @@
         <v>409</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C80" s="1">
         <v>2450</v>
@@ -15905,7 +15901,7 @@
         <v>410</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C81" s="1">
         <v>1750</v>
@@ -15921,7 +15917,7 @@
         <v>411</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C82" s="1">
         <v>2800</v>
@@ -15937,7 +15933,7 @@
         <v>412</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C83" s="1">
         <v>1750</v>
@@ -15953,7 +15949,7 @@
         <v>413</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C84" s="1">
         <v>1750</v>
@@ -15969,7 +15965,7 @@
         <v>414</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="C85" s="1">
         <v>2100</v>
@@ -15985,7 +15981,7 @@
         <v>415</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C86" s="1">
         <v>1050</v>
@@ -16001,7 +15997,7 @@
         <v>416</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C87" s="1">
         <v>50</v>
@@ -16017,7 +16013,7 @@
         <v>417</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C88" s="1">
         <v>130</v>
@@ -16033,7 +16029,7 @@
         <v>418</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C89" s="1">
         <v>280</v>
@@ -16048,7 +16044,7 @@
         <v>419</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="C90" s="1">
         <v>280</v>
@@ -16064,7 +16060,7 @@
         <v>420</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="C91" s="1">
         <v>1750</v>
@@ -16080,7 +16076,7 @@
         <v>421</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="C92" s="1">
         <v>1750</v>
@@ -16096,7 +16092,7 @@
         <v>422</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C93" s="1">
         <v>1400</v>
@@ -16112,7 +16108,7 @@
         <v>423</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C94" s="1">
         <v>600</v>
@@ -16128,7 +16124,7 @@
         <v>424</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="C95" s="1">
         <v>3550</v>
@@ -16144,7 +16140,7 @@
         <v>425</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C96" s="1">
         <v>2800</v>
@@ -16160,7 +16156,7 @@
         <v>426</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="C97" s="1">
         <v>700</v>
@@ -16176,7 +16172,7 @@
         <v>427</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="C98" s="1">
         <v>200</v>
@@ -16192,7 +16188,7 @@
         <v>428</v>
       </c>
       <c r="B99" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C99">
         <v>1100</v>
@@ -16208,7 +16204,7 @@
         <v>429</v>
       </c>
       <c r="B100" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C100">
         <v>1750</v>
@@ -16224,7 +16220,7 @@
         <v>430</v>
       </c>
       <c r="B101" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C101">
         <v>2700</v>

--- a/inventario.xlsx.xlsx
+++ b/inventario.xlsx.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2746fa196ce476c0/Desktop/kiosco el tio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="204" documentId="11_F0BF34C6AB674EABCA5660F4A3CFFCC672003DE8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0F7CA3BE-0132-4877-95E1-F57AF83A4B42}"/>
+  <xr:revisionPtr revIDLastSave="205" documentId="11_F0BF34C6AB674EABCA5660F4A3CFFCC672003DE8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CB503E31-D176-4DC9-9A32-E9EF3799B95C}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1362,7 +1362,7 @@
     <t>YERBA MAÑANITA 500G</t>
   </si>
   <si>
-    <t xml:space="preserve">JABON LIQUIDO DRANBY </t>
+    <t xml:space="preserve">JABON LIQUIDO GRANBY </t>
   </si>
 </sst>
 </file>
@@ -1429,6 +1429,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>

--- a/inventario.xlsx.xlsx
+++ b/inventario.xlsx.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2746fa196ce476c0/Desktop/kiosco el tio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="205" documentId="11_F0BF34C6AB674EABCA5660F4A3CFFCC672003DE8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CB503E31-D176-4DC9-9A32-E9EF3799B95C}"/>
+  <xr:revisionPtr revIDLastSave="221" documentId="11_F0BF34C6AB674EABCA5660F4A3CFFCC672003DE8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0AC4AC4F-1886-4DC1-B658-677480869D67}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Comestibles" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="457" uniqueCount="442">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="458" uniqueCount="443">
   <si>
     <t>CODIGO</t>
   </si>
@@ -285,9 +285,6 @@
     <t>QUILMES 1890 1L RET</t>
   </si>
   <si>
-    <t>PAN DE HAMBURGUESA DON YEYO</t>
-  </si>
-  <si>
     <t>MANA SIMPLE</t>
   </si>
   <si>
@@ -372,9 +369,6 @@
     <t>ALFAJOR TRIPLE TINCHO</t>
   </si>
   <si>
-    <t>CREMA LECHE 200G</t>
-  </si>
-  <si>
     <t>ALFAJOR TRIPLE LAS COLONIAS</t>
   </si>
   <si>
@@ -1363,6 +1357,15 @@
   </si>
   <si>
     <t xml:space="preserve">JABON LIQUIDO GRANBY </t>
+  </si>
+  <si>
+    <t>PAN DE HAMBURGUESA DON YEYO GDE</t>
+  </si>
+  <si>
+    <t>CREMA LECHE TREGAR 200G</t>
+  </si>
+  <si>
+    <t>CREMA LECHE ECONOMICA 200G</t>
   </si>
 </sst>
 </file>
@@ -1857,11 +1860,11 @@
         <v>48</v>
       </c>
       <c r="C14" s="1">
-        <v>2000</v>
+        <v>2400</v>
       </c>
       <c r="D14" s="1">
         <f t="shared" si="0"/>
-        <v>2800</v>
+        <v>3400</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -1982,7 +1985,7 @@
         <v>21</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="C22" s="1">
         <v>1950</v>
@@ -1998,14 +2001,14 @@
         <v>22</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>82</v>
+        <v>440</v>
       </c>
       <c r="C23" s="1">
-        <v>2600</v>
+        <v>2400</v>
       </c>
       <c r="D23" s="1">
         <f t="shared" si="0"/>
-        <v>3700</v>
+        <v>3400</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -2014,14 +2017,14 @@
         <v>23</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C24" s="1">
-        <v>2250</v>
+        <v>2560</v>
       </c>
       <c r="D24" s="1">
         <f t="shared" si="0"/>
-        <v>3200</v>
+        <v>3600</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -2030,7 +2033,7 @@
         <v>24</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C25" s="1">
         <v>1550</v>
@@ -2046,7 +2049,7 @@
         <v>25</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C26" s="1">
         <v>2850</v>
@@ -2062,7 +2065,7 @@
         <v>26</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C27" s="1">
         <v>7100</v>
@@ -2078,7 +2081,7 @@
         <v>27</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C28" s="1">
         <v>2500</v>
@@ -2094,7 +2097,7 @@
         <v>28</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C29">
         <v>4250</v>
@@ -2110,7 +2113,7 @@
         <v>29</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C30" s="1">
         <v>10650</v>
@@ -2126,14 +2129,14 @@
         <v>30</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>111</v>
+        <v>441</v>
       </c>
       <c r="C31" s="1">
-        <v>2100</v>
+        <v>2300</v>
       </c>
       <c r="D31" s="1">
         <f t="shared" si="0"/>
-        <v>3000</v>
+        <v>3300</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -2142,7 +2145,7 @@
         <v>31</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C32" s="1">
         <v>1800</v>
@@ -2158,7 +2161,7 @@
         <v>32</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C33" s="1">
         <v>1200</v>
@@ -2174,7 +2177,7 @@
         <v>33</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C34" s="1">
         <v>1500</v>
@@ -2190,7 +2193,7 @@
         <v>34</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C35" s="1">
         <v>1250</v>
@@ -2206,7 +2209,7 @@
         <v>35</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C36" s="1">
         <v>1250</v>
@@ -2222,7 +2225,7 @@
         <v>36</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C37" s="1">
         <v>1050</v>
@@ -2238,7 +2241,7 @@
         <v>37</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C38" s="1">
         <v>2800</v>
@@ -2254,7 +2257,7 @@
         <v>38</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C39" s="1">
         <v>3200</v>
@@ -2270,7 +2273,7 @@
         <v>39</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C40" s="1">
         <v>11400</v>
@@ -2286,7 +2289,7 @@
         <v>40</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C41" s="1">
         <v>9950</v>
@@ -2302,7 +2305,7 @@
         <v>41</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C42" s="1">
         <v>5350</v>
@@ -2318,7 +2321,7 @@
         <v>42</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C43" s="1">
         <v>1050</v>
@@ -2334,7 +2337,7 @@
         <v>43</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C44" s="1">
         <v>900</v>
@@ -2350,7 +2353,7 @@
         <v>44</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C45" s="1">
         <v>800</v>
@@ -2366,7 +2369,7 @@
         <v>45</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C46" s="1">
         <v>600</v>
@@ -2382,7 +2385,7 @@
         <v>46</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C47" s="1">
         <v>1400</v>
@@ -2398,7 +2401,7 @@
         <v>47</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C48" s="1">
         <v>1750</v>
@@ -2414,7 +2417,7 @@
         <v>48</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C49" s="1">
         <v>2800</v>
@@ -2430,7 +2433,7 @@
         <v>49</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="51" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -2439,7 +2442,7 @@
         <v>50</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C51" s="1">
         <v>1550</v>
@@ -2455,7 +2458,7 @@
         <v>51</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C52" s="1">
         <v>1750</v>
@@ -2471,7 +2474,7 @@
         <v>52</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="D53" s="1" t="str">
         <f t="shared" si="2"/>
@@ -2484,7 +2487,7 @@
         <v>53</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C54" s="1">
         <v>3900</v>
@@ -2500,7 +2503,7 @@
         <v>54</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C55" s="1">
         <v>1400</v>
@@ -2516,7 +2519,7 @@
         <v>55</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C56" s="1">
         <v>700</v>
@@ -2532,7 +2535,7 @@
         <v>56</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C57" s="1">
         <v>1100</v>
@@ -2548,7 +2551,7 @@
         <v>57</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C58" s="1">
         <v>700</v>
@@ -2564,7 +2567,7 @@
         <v>58</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C59" s="1">
         <v>450</v>
@@ -2580,7 +2583,7 @@
         <v>59</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="D60" s="1" t="str">
         <f t="shared" si="2"/>
@@ -2593,7 +2596,7 @@
         <v>60</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="C61" s="1">
         <v>700</v>
@@ -2609,7 +2612,7 @@
         <v>61</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C62" s="1">
         <v>1400</v>
@@ -2625,7 +2628,7 @@
         <v>62</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="C63" s="1">
         <v>700</v>
@@ -2641,7 +2644,7 @@
         <v>63</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C64" s="1">
         <v>2000</v>
@@ -2657,7 +2660,7 @@
         <v>64</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C65" s="1">
         <v>1550</v>
@@ -2673,7 +2676,7 @@
         <v>65</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C66" s="1">
         <v>1400</v>
@@ -2689,7 +2692,7 @@
         <v>66</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C67" s="1">
         <v>1250</v>
@@ -2705,7 +2708,7 @@
         <v>67</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C68" s="1">
         <v>1950</v>
@@ -2721,7 +2724,7 @@
         <v>68</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C69" s="1">
         <v>1400</v>
@@ -2737,7 +2740,7 @@
         <v>69</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C70" s="1">
         <v>1250</v>
@@ -2753,7 +2756,7 @@
         <v>70</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C71" s="1">
         <v>750</v>
@@ -2769,7 +2772,7 @@
         <v>71</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="C72">
         <v>1400</v>
@@ -2785,7 +2788,7 @@
         <v>72</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C73" s="1">
         <v>1400</v>
@@ -2801,7 +2804,7 @@
         <v>73</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C74" s="1">
         <v>1050</v>
@@ -2817,7 +2820,7 @@
         <v>74</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="D75" s="1" t="str">
         <f t="shared" si="2"/>
@@ -2830,7 +2833,7 @@
         <v>75</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="D76" s="1" t="str">
         <f t="shared" si="2"/>
@@ -2843,7 +2846,7 @@
         <v>76</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C77" s="1">
         <v>450</v>
@@ -2859,7 +2862,7 @@
         <v>77</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C78" s="1">
         <v>1050</v>
@@ -2875,7 +2878,7 @@
         <v>78</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="C79" s="1">
         <v>1050</v>
@@ -2891,7 +2894,7 @@
         <v>79</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="C80" s="1">
         <v>1400</v>
@@ -2907,7 +2910,7 @@
         <v>80</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C81" s="1">
         <v>1750</v>
@@ -2923,7 +2926,7 @@
         <v>81</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="C82" s="1">
         <v>1050</v>
@@ -2939,7 +2942,7 @@
         <v>82</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="C83" s="1">
         <v>1050</v>
@@ -2955,7 +2958,7 @@
         <v>83</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C84" s="1">
         <v>1400</v>
@@ -2971,7 +2974,7 @@
         <v>84</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="C85" s="1">
         <v>700</v>
@@ -2987,7 +2990,7 @@
         <v>85</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="C86" s="1">
         <v>1400</v>
@@ -3003,7 +3006,7 @@
         <v>86</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="C87" s="1">
         <v>550</v>
@@ -3019,7 +3022,7 @@
         <v>87</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="C88" s="1">
         <v>800</v>
@@ -3035,7 +3038,7 @@
         <v>88</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C89" s="1">
         <v>1050</v>
@@ -3051,7 +3054,7 @@
         <v>89</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C90" s="1">
         <v>1050</v>
@@ -3067,7 +3070,7 @@
         <v>90</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="C91" s="1">
         <v>2500</v>
@@ -3083,7 +3086,7 @@
         <v>91</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="C92" s="1">
         <v>800</v>
@@ -3099,7 +3102,7 @@
         <v>92</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="C93" s="1">
         <v>1200</v>
@@ -3115,7 +3118,7 @@
         <v>93</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="C94" s="1">
         <v>700</v>
@@ -3131,7 +3134,7 @@
         <v>94</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="C95" s="1">
         <v>1400</v>
@@ -3147,7 +3150,7 @@
         <v>95</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="C96" s="1">
         <v>1050</v>
@@ -3163,7 +3166,7 @@
         <v>96</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C97" s="1">
         <v>1400</v>
@@ -3179,7 +3182,7 @@
         <v>97</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="C98" s="1">
         <v>1050</v>
@@ -3195,7 +3198,7 @@
         <v>98</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C99" s="1">
         <v>600</v>
@@ -3211,7 +3214,7 @@
         <v>99</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="C100" s="1">
         <v>1050</v>
@@ -3227,7 +3230,7 @@
         <v>100</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="C101" s="1">
         <v>4100</v>
@@ -3243,7 +3246,7 @@
         <v>101</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="C102" s="1">
         <v>1750</v>
@@ -3259,7 +3262,7 @@
         <v>102</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="C103" s="1">
         <v>1750</v>
@@ -3275,7 +3278,7 @@
         <v>103</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="C104" s="1">
         <v>600</v>
@@ -3291,7 +3294,7 @@
         <v>104</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C105" s="1">
         <v>2250</v>
@@ -3307,7 +3310,7 @@
         <v>105</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="C106" s="1">
         <v>2600</v>
@@ -3323,7 +3326,7 @@
         <v>106</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="C107" s="1">
         <v>1100</v>
@@ -3339,7 +3342,7 @@
         <v>107</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="C108" s="1">
         <v>1050</v>
@@ -3355,7 +3358,7 @@
         <v>108</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="C109" s="1">
         <v>1050</v>
@@ -3371,7 +3374,7 @@
         <v>109</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="C110" s="1">
         <v>1400</v>
@@ -3387,7 +3390,7 @@
         <v>110</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="C111" s="1">
         <v>2100</v>
@@ -3403,7 +3406,7 @@
         <v>111</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="C112" s="1">
         <v>1600</v>
@@ -3419,7 +3422,7 @@
         <v>112</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="C113" s="1">
         <v>1750</v>
@@ -3435,7 +3438,7 @@
         <v>113</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="C114" s="1">
         <v>900</v>
@@ -3451,7 +3454,7 @@
         <v>114</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C115" s="1">
         <v>1200</v>
@@ -3467,7 +3470,7 @@
         <v>115</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="C116" s="1">
         <v>1200</v>
@@ -3483,7 +3486,7 @@
         <v>116</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="C117" s="1">
         <v>200</v>
@@ -3499,7 +3502,7 @@
         <v>117</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="C118" s="1">
         <v>1400</v>
@@ -3515,7 +3518,7 @@
         <v>118</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="C119" s="1">
         <v>900</v>
@@ -3531,7 +3534,7 @@
         <v>119</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="C120" s="1">
         <v>1250</v>
@@ -3547,7 +3550,7 @@
         <v>120</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="C121">
         <v>1750</v>
@@ -3563,7 +3566,7 @@
         <v>121</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="C122" s="1">
         <v>1100</v>
@@ -3579,7 +3582,7 @@
         <v>122</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="C123" s="1">
         <v>2300</v>
@@ -3595,7 +3598,7 @@
         <v>123</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="C124" s="1">
         <v>1750</v>
@@ -3611,7 +3614,7 @@
         <v>124</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="C125" s="1">
         <v>2450</v>
@@ -3627,7 +3630,7 @@
         <v>125</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="C126" s="1">
         <v>250</v>
@@ -3643,7 +3646,7 @@
         <v>126</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="C127" s="1">
         <v>2300</v>
@@ -3659,7 +3662,7 @@
         <v>127</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="D128" s="1">
         <v>150</v>
@@ -3671,7 +3674,7 @@
         <v>128</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="D129" s="1">
         <v>150</v>
@@ -3683,10 +3686,10 @@
         <v>129</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="C130" s="1" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="D130" s="1">
         <v>150</v>
@@ -3698,7 +3701,7 @@
         <v>130</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="D131" s="1">
         <v>200</v>
@@ -3710,7 +3713,7 @@
         <v>131</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="D132" s="1">
         <v>100</v>
@@ -3722,7 +3725,7 @@
         <v>132</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="D133" s="1">
         <v>100</v>
@@ -3734,7 +3737,7 @@
         <v>133</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="C134" s="1">
         <v>1750</v>
@@ -3750,7 +3753,7 @@
         <v>134</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="C135" s="1">
         <v>1650</v>
@@ -3766,7 +3769,7 @@
         <v>135</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="C136" s="1">
         <v>600</v>
@@ -3782,7 +3785,7 @@
         <v>136</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="C137" s="1">
         <v>1450</v>
@@ -3798,7 +3801,7 @@
         <v>137</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="C138" s="1">
         <v>550</v>
@@ -3814,7 +3817,7 @@
         <v>138</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="C139" s="1">
         <v>1200</v>
@@ -3830,7 +3833,7 @@
         <v>139</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="C140" s="1">
         <v>400</v>
@@ -3846,7 +3849,7 @@
         <v>140</v>
       </c>
       <c r="B141" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="C141">
         <v>1750</v>
@@ -3862,7 +3865,7 @@
         <v>141</v>
       </c>
       <c r="B142" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="C142">
         <v>1400</v>
@@ -3878,7 +3881,7 @@
         <v>142</v>
       </c>
       <c r="B143" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="C143">
         <v>1550</v>
@@ -3893,15 +3896,21 @@
         <f t="shared" si="4"/>
         <v>143</v>
       </c>
-      <c r="D144" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="B144" t="s">
+        <v>442</v>
+      </c>
+      <c r="C144">
+        <v>2000</v>
+      </c>
+      <c r="D144" s="1">
+        <f t="shared" si="3"/>
+        <v>2800</v>
       </c>
     </row>
     <row r="145" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A145" s="1" t="str">
+      <c r="A145" s="1">
         <f t="shared" si="4"/>
-        <v/>
+        <v>144</v>
       </c>
       <c r="D145" s="1" t="str">
         <f t="shared" si="3"/>
@@ -8802,7 +8811,7 @@
         <v>163</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C25" s="1">
         <v>2850</v>
@@ -8818,7 +8827,7 @@
         <v>164</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C26" s="1">
         <v>2500</v>
@@ -8834,7 +8843,7 @@
         <v>165</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C27" s="1">
         <v>2100</v>
@@ -8850,7 +8859,7 @@
         <v>166</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C28" s="1">
         <v>1400</v>
@@ -8866,7 +8875,7 @@
         <v>167</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C29" s="1">
         <v>1250</v>
@@ -8882,7 +8891,7 @@
         <v>168</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C30" s="1">
         <v>2500</v>
@@ -8898,7 +8907,7 @@
         <v>169</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C31" s="1">
         <v>2500</v>
@@ -8914,7 +8923,7 @@
         <v>170</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D32" s="1" t="str">
         <f t="shared" si="0"/>
@@ -8927,7 +8936,7 @@
         <v>171</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C33" s="1">
         <v>2500</v>
@@ -8943,7 +8952,7 @@
         <v>172</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D34" s="1" t="str">
         <f t="shared" si="0"/>
@@ -8956,7 +8965,7 @@
         <v>173</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D35" s="1" t="str">
         <f t="shared" si="0"/>
@@ -8969,7 +8978,7 @@
         <v>174</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C36" s="1">
         <v>1250</v>
@@ -8985,7 +8994,7 @@
         <v>175</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C37" s="1">
         <v>1750</v>
@@ -9001,7 +9010,7 @@
         <v>176</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C38" s="1">
         <v>1500</v>
@@ -9017,7 +9026,7 @@
         <v>177</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C39" s="1">
         <v>1100</v>
@@ -9033,7 +9042,7 @@
         <v>178</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="D40" s="1" t="str">
         <f t="shared" si="0"/>
@@ -9046,7 +9055,7 @@
         <v>179</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C41" s="1">
         <v>1750</v>
@@ -9062,7 +9071,7 @@
         <v>180</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C42" s="1">
         <v>1500</v>
@@ -9078,7 +9087,7 @@
         <v>181</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C43" s="1">
         <v>1100</v>
@@ -9094,7 +9103,7 @@
         <v>182</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D44" s="1" t="str">
         <f t="shared" si="0"/>
@@ -9107,7 +9116,7 @@
         <v>183</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C45" s="1">
         <v>1400</v>
@@ -9123,7 +9132,7 @@
         <v>184</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="D46" s="1" t="str">
         <f t="shared" si="0"/>
@@ -9136,7 +9145,7 @@
         <v>185</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C47" s="1">
         <v>2100</v>
@@ -9152,7 +9161,7 @@
         <v>186</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="D48" s="1" t="str">
         <f t="shared" si="0"/>
@@ -9165,7 +9174,7 @@
         <v>187</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D49" s="1" t="str">
         <f t="shared" si="0"/>
@@ -9178,7 +9187,7 @@
         <v>188</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="C50" s="1">
         <v>1250</v>
@@ -9194,7 +9203,7 @@
         <v>189</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C51" s="1">
         <v>1750</v>
@@ -9210,7 +9219,7 @@
         <v>190</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C52" s="1">
         <v>1400</v>
@@ -9226,7 +9235,7 @@
         <v>191</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C53" s="1">
         <v>1150</v>
@@ -9242,7 +9251,7 @@
         <v>192</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="D54" s="1" t="str">
         <f t="shared" si="0"/>
@@ -9255,7 +9264,7 @@
         <v>193</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C55" s="1">
         <v>900</v>
@@ -9271,7 +9280,7 @@
         <v>194</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="C56" s="1">
         <v>1400</v>
@@ -9287,7 +9296,7 @@
         <v>195</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C57" s="1">
         <v>2750</v>
@@ -9303,7 +9312,7 @@
         <v>196</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C58" s="1">
         <v>1000</v>
@@ -9319,7 +9328,7 @@
         <v>197</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C59" s="1">
         <v>550</v>
@@ -9335,7 +9344,7 @@
         <v>198</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C60" s="1">
         <v>1000</v>
@@ -9351,7 +9360,7 @@
         <v>199</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C61" s="1">
         <v>1250</v>
@@ -9367,7 +9376,7 @@
         <v>200</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="D62" s="1" t="str">
         <f t="shared" si="0"/>
@@ -9380,7 +9389,7 @@
         <v>201</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C63">
         <v>2100</v>
@@ -9396,7 +9405,7 @@
         <v>202</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="D64" s="1" t="str">
         <f t="shared" si="0"/>
@@ -9409,7 +9418,7 @@
         <v>203</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="C65" s="1">
         <v>2100</v>
@@ -9425,7 +9434,7 @@
         <v>204</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D66" s="1" t="str">
         <f t="shared" si="0"/>
@@ -9438,7 +9447,7 @@
         <v>205</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="C67">
         <v>2750</v>
@@ -9454,7 +9463,7 @@
         <v>206</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="C68" s="1">
         <v>2500</v>
@@ -9470,7 +9479,7 @@
         <v>207</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="D69" s="1" t="str">
         <f t="shared" si="0"/>
@@ -9483,7 +9492,7 @@
         <v>208</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="C70" s="1">
         <v>2500</v>
@@ -9499,7 +9508,7 @@
         <v>209</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="C71" s="1">
         <v>1950</v>
@@ -9515,7 +9524,7 @@
         <v>210</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="C72" s="1">
         <v>550</v>
@@ -9531,7 +9540,7 @@
         <v>211</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C73" s="1">
         <v>550</v>
@@ -9547,7 +9556,7 @@
         <v>212</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C74" s="1">
         <v>400</v>
@@ -9563,7 +9572,7 @@
         <v>213</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="D75" s="1" t="str">
         <f t="shared" si="0"/>
@@ -9576,7 +9585,7 @@
         <v>214</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="C76" s="1">
         <v>1750</v>
@@ -9592,7 +9601,7 @@
         <v>215</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D77" s="1" t="str">
         <f t="shared" si="0"/>
@@ -9605,7 +9614,7 @@
         <v>216</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="C78" s="1">
         <v>1750</v>
@@ -9621,7 +9630,7 @@
         <v>217</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="C79" s="1">
         <v>2350</v>
@@ -9637,7 +9646,7 @@
         <v>218</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="C80" s="1">
         <v>1400</v>
@@ -9653,7 +9662,7 @@
         <v>219</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="C81" s="1">
         <v>2500</v>
@@ -10636,7 +10645,7 @@
     </row>
     <row r="3" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
-        <f t="shared" ref="A3:A54" si="1">IF(B2&lt;&gt;"", A2+1, "")</f>
+        <f t="shared" ref="A3:A56" si="1">IF(B2&lt;&gt;"", A2+1, "")</f>
         <v>221</v>
       </c>
       <c r="B3" s="1" t="s">
@@ -10784,7 +10793,7 @@
         <v>230</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C12" s="1">
         <v>2050</v>
@@ -10800,7 +10809,7 @@
         <v>231</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C13" s="1">
         <v>1300</v>
@@ -10816,7 +10825,7 @@
         <v>232</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C14" s="1">
         <v>3000</v>
@@ -10832,7 +10841,7 @@
         <v>233</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D15" s="1" t="str">
         <f t="shared" si="0"/>
@@ -10845,7 +10854,7 @@
         <v>234</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D16" s="1" t="str">
         <f t="shared" si="0"/>
@@ -10858,7 +10867,7 @@
         <v>235</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C17" s="1">
         <v>2000</v>
@@ -10874,7 +10883,7 @@
         <v>236</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C18" s="1">
         <v>3900</v>
@@ -10890,7 +10899,7 @@
         <v>237</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="D19" s="1" t="str">
         <f t="shared" si="0"/>
@@ -10903,7 +10912,7 @@
         <v>238</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C20" s="1">
         <v>2850</v>
@@ -10919,7 +10928,7 @@
         <v>239</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D21" s="1" t="str">
         <f t="shared" si="0"/>
@@ -10932,7 +10941,7 @@
         <v>240</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="C22">
         <v>1750</v>
@@ -10948,7 +10957,7 @@
         <v>241</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C23" s="1">
         <v>4050</v>
@@ -10964,7 +10973,7 @@
         <v>242</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C24" s="1">
         <v>3200</v>
@@ -10980,7 +10989,7 @@
         <v>243</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C25" s="1">
         <v>1750</v>
@@ -10996,7 +11005,7 @@
         <v>244</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C26" s="1">
         <v>4600</v>
@@ -11012,7 +11021,7 @@
         <v>245</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C27" s="1">
         <v>4450</v>
@@ -11028,7 +11037,7 @@
         <v>246</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C28" s="1">
         <v>3200</v>
@@ -11044,7 +11053,7 @@
         <v>247</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C29" s="1">
         <v>3050</v>
@@ -11060,7 +11069,7 @@
         <v>248</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C30" s="1">
         <v>2500</v>
@@ -11076,7 +11085,7 @@
         <v>249</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C31" s="1">
         <v>2800</v>
@@ -11092,7 +11101,7 @@
         <v>250</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="C32" s="1">
         <v>2250</v>
@@ -11108,7 +11117,7 @@
         <v>251</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C33" s="1">
         <v>1750</v>
@@ -11124,7 +11133,7 @@
         <v>252</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="C34">
         <v>2500</v>
@@ -11140,7 +11149,7 @@
         <v>253</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C35" s="1">
         <v>2100</v>
@@ -11156,7 +11165,7 @@
         <v>254</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C36" s="1">
         <v>1750</v>
@@ -11172,7 +11181,7 @@
         <v>255</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C37" s="1">
         <v>1550</v>
@@ -11188,7 +11197,7 @@
         <v>256</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C38" s="1">
         <v>1400</v>
@@ -11204,7 +11213,7 @@
         <v>257</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C39" s="1">
         <v>1250</v>
@@ -11220,7 +11229,7 @@
         <v>258</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="C40" s="1">
         <v>1100</v>
@@ -11236,7 +11245,7 @@
         <v>259</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="C41" s="1">
         <v>15650</v>
@@ -11252,7 +11261,7 @@
         <v>260</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="C42" s="1">
         <v>10000</v>
@@ -11268,7 +11277,7 @@
         <v>261</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="C43" s="1">
         <v>6750</v>
@@ -11284,7 +11293,7 @@
         <v>262</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="C44" s="1">
         <v>3900</v>
@@ -11300,7 +11309,7 @@
         <v>263</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="D45" s="1" t="str">
         <f t="shared" si="0"/>
@@ -11313,7 +11322,7 @@
         <v>264</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="D46" s="1" t="str">
         <f t="shared" si="0"/>
@@ -11326,7 +11335,7 @@
         <v>265</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="C47" s="1">
         <v>3500</v>
@@ -11342,7 +11351,7 @@
         <v>266</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="C48" s="1">
         <v>1200</v>
@@ -11358,7 +11367,7 @@
         <v>267</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="C49" s="1">
         <v>800</v>
@@ -11374,7 +11383,7 @@
         <v>268</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="C50" s="1">
         <v>1050</v>
@@ -11390,7 +11399,7 @@
         <v>269</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="C51" s="1">
         <v>800</v>
@@ -11406,7 +11415,7 @@
         <v>270</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="C52" s="1">
         <v>7750</v>
@@ -11422,7 +11431,7 @@
         <v>271</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="C53" s="1">
         <v>4600</v>
@@ -11438,7 +11447,7 @@
         <v>272</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="C54" s="1">
         <v>3900</v>
@@ -11449,6 +11458,10 @@
       </c>
     </row>
     <row r="55" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="1">
+        <f t="shared" si="1"/>
+        <v>273</v>
+      </c>
       <c r="D55" s="1" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -11456,7 +11469,7 @@
     </row>
     <row r="56" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="str">
-        <f t="shared" ref="A56:A81" si="2">IF(B55&lt;&gt;"", A55+1, "")</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="D56" s="1" t="str">
@@ -11466,7 +11479,7 @@
     </row>
     <row r="57" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="A57:A81" si="2">IF(B56&lt;&gt;"", A56+1, "")</f>
         <v/>
       </c>
       <c r="D57" s="1" t="str">
@@ -13059,7 +13072,7 @@
         <v>297</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C26" s="1">
         <v>1050</v>
@@ -13075,7 +13088,7 @@
         <v>298</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C27" s="1">
         <v>1100</v>
@@ -13091,7 +13104,7 @@
         <v>299</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C28" s="1">
         <v>1100</v>
@@ -13107,7 +13120,7 @@
         <v>300</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C29" s="1">
         <v>1100</v>
@@ -13123,7 +13136,7 @@
         <v>301</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C30" s="1">
         <v>1550</v>
@@ -13139,7 +13152,7 @@
         <v>302</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C31" s="1">
         <v>2000</v>
@@ -13155,7 +13168,7 @@
         <v>303</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C32" s="1">
         <v>700</v>
@@ -13171,7 +13184,7 @@
         <v>304</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C33" s="1">
         <v>1400</v>
@@ -13187,7 +13200,7 @@
         <v>305</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C34" s="1">
         <v>400</v>
@@ -13203,7 +13216,7 @@
         <v>306</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C35" s="1">
         <v>550</v>
@@ -13219,7 +13232,7 @@
         <v>307</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C36" s="1">
         <v>380</v>
@@ -13235,7 +13248,7 @@
         <v>308</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C37" s="1">
         <v>700</v>
@@ -13251,7 +13264,7 @@
         <v>309</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C38" s="1">
         <v>1300</v>
@@ -13267,7 +13280,7 @@
         <v>310</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C39" s="1">
         <v>1400</v>
@@ -13283,7 +13296,7 @@
         <v>311</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C40" s="1">
         <v>300</v>
@@ -13299,7 +13312,7 @@
         <v>312</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C41" s="1">
         <v>1050</v>
@@ -13315,7 +13328,7 @@
         <v>313</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C42" s="1">
         <v>500</v>
@@ -13331,7 +13344,7 @@
         <v>314</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C43" s="1">
         <v>1750</v>
@@ -13347,7 +13360,7 @@
         <v>315</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C44" s="1">
         <v>1050</v>
@@ -13363,7 +13376,7 @@
         <v>316</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C45" s="1">
         <v>3150</v>
@@ -13379,7 +13392,7 @@
         <v>317</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C46" s="1">
         <v>3900</v>
@@ -13395,7 +13408,7 @@
         <v>318</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C47" s="1">
         <v>800</v>
@@ -13411,7 +13424,7 @@
         <v>319</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C48" s="1">
         <v>800</v>
@@ -13427,7 +13440,7 @@
         <v>320</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C49" s="1">
         <v>400</v>
@@ -13443,7 +13456,7 @@
         <v>321</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C50" s="1">
         <v>550</v>
@@ -13459,7 +13472,7 @@
         <v>322</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C51" s="1">
         <v>200</v>
@@ -13475,7 +13488,7 @@
         <v>323</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C52" s="1">
         <v>100</v>
@@ -13491,7 +13504,7 @@
         <v>324</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D53" s="1">
         <v>50</v>
@@ -13503,7 +13516,7 @@
         <v>325</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C54" s="1">
         <v>50</v>
@@ -13519,7 +13532,7 @@
         <v>326</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C55" s="1">
         <v>50</v>
@@ -13535,7 +13548,7 @@
         <v>327</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D56" s="1">
         <v>50</v>
@@ -13547,7 +13560,7 @@
         <v>328</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C57" s="1">
         <v>250</v>
@@ -13563,7 +13576,7 @@
         <v>329</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C58" s="1">
         <v>100</v>
@@ -13579,7 +13592,7 @@
         <v>330</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C59" s="1">
         <v>250</v>
@@ -13595,7 +13608,7 @@
         <v>331</v>
       </c>
       <c r="B60" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="C60">
         <v>2250</v>
@@ -13611,7 +13624,7 @@
         <v>332</v>
       </c>
       <c r="B61" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="C61">
         <v>1050</v>
@@ -13627,7 +13640,7 @@
         <v>333</v>
       </c>
       <c r="B62" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="C62">
         <v>550</v>
@@ -14642,7 +14655,7 @@
         <v>331</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="C2" s="1">
         <v>550</v>
@@ -14658,7 +14671,7 @@
         <v>332</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="C3" s="1">
         <v>1100</v>
@@ -14674,7 +14687,7 @@
         <v>333</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="C4" s="1">
         <v>850</v>
@@ -14690,7 +14703,7 @@
         <v>334</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="C5" s="1">
         <v>1400</v>
@@ -14706,7 +14719,7 @@
         <v>335</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="C6" s="1">
         <v>600</v>
@@ -14722,7 +14735,7 @@
         <v>336</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="C7" s="1">
         <v>900</v>
@@ -14738,7 +14751,7 @@
         <v>337</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="C8" s="1">
         <v>1550</v>
@@ -14754,7 +14767,7 @@
         <v>338</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="C9" s="1">
         <v>3550</v>
@@ -14770,7 +14783,7 @@
         <v>339</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="C10" s="1">
         <v>1400</v>
@@ -14786,7 +14799,7 @@
         <v>340</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C11" s="1">
         <v>2000</v>
@@ -14802,7 +14815,7 @@
         <v>341</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="C12" s="1">
         <v>1400</v>
@@ -14818,7 +14831,7 @@
         <v>342</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="C13" s="1">
         <v>1150</v>
@@ -14834,7 +14847,7 @@
         <v>343</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="C14" s="1">
         <v>1750</v>
@@ -14850,7 +14863,7 @@
         <v>344</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C15" s="1">
         <v>1750</v>
@@ -14866,7 +14879,7 @@
         <v>345</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="C16" s="1">
         <v>1050</v>
@@ -14882,7 +14895,7 @@
         <v>346</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="C17" s="1">
         <v>2800</v>
@@ -14898,7 +14911,7 @@
         <v>347</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="C18" s="1">
         <v>2500</v>
@@ -14914,7 +14927,7 @@
         <v>348</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="C19" s="1">
         <v>3150</v>
@@ -14930,7 +14943,7 @@
         <v>349</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="C20" s="1">
         <v>4250</v>
@@ -14946,7 +14959,7 @@
         <v>350</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="C21" s="1">
         <v>1200</v>
@@ -14962,7 +14975,7 @@
         <v>351</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C22" s="1">
         <v>1050</v>
@@ -14978,7 +14991,7 @@
         <v>352</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="C23" s="1">
         <v>1050</v>
@@ -14994,7 +15007,7 @@
         <v>353</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="C24" s="1">
         <v>600</v>
@@ -15010,7 +15023,7 @@
         <v>354</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="C25" s="1">
         <v>1050</v>
@@ -15026,7 +15039,7 @@
         <v>355</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="C26" s="1">
         <v>5300</v>
@@ -15042,7 +15055,7 @@
         <v>356</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="C27" s="1">
         <v>4600</v>
@@ -15058,7 +15071,7 @@
         <v>357</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="C28" s="1">
         <v>2100</v>
@@ -15074,7 +15087,7 @@
         <v>358</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="C29" s="1">
         <v>1700</v>
@@ -15090,7 +15103,7 @@
         <v>359</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="C30" s="1">
         <v>2750</v>
@@ -15106,7 +15119,7 @@
         <v>360</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="C31" s="1">
         <v>3500</v>
@@ -15122,7 +15135,7 @@
         <v>361</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="C32" s="1">
         <v>230</v>
@@ -15137,7 +15150,7 @@
         <v>362</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C33" s="1">
         <v>3200</v>
@@ -15153,7 +15166,7 @@
         <v>363</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="C34" s="1">
         <v>1900</v>
@@ -15169,7 +15182,7 @@
         <v>364</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="C35" s="1">
         <v>2100</v>
@@ -15185,7 +15198,7 @@
         <v>365</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="C36" s="1">
         <v>1750</v>
@@ -15201,7 +15214,7 @@
         <v>366</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C37" s="1">
         <v>2100</v>
@@ -15217,7 +15230,7 @@
         <v>367</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="C38" s="1">
         <v>2450</v>
@@ -15233,7 +15246,7 @@
         <v>368</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="C39" s="1">
         <v>3200</v>
@@ -15249,7 +15262,7 @@
         <v>369</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="C40" s="1">
         <v>3200</v>
@@ -15265,7 +15278,7 @@
         <v>370</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="C41" s="1">
         <v>2800</v>
@@ -15281,7 +15294,7 @@
         <v>371</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C42" s="1">
         <v>1050</v>
@@ -15297,7 +15310,7 @@
         <v>372</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="C43" s="1">
         <v>1050</v>
@@ -15313,7 +15326,7 @@
         <v>373</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="C44" s="1">
         <v>300</v>
@@ -15329,7 +15342,7 @@
         <v>374</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="C45" s="1">
         <v>230</v>
@@ -15345,7 +15358,7 @@
         <v>375</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="C46" s="1">
         <v>2100</v>
@@ -15361,7 +15374,7 @@
         <v>376</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="C47" s="1">
         <v>2450</v>
@@ -15377,7 +15390,7 @@
         <v>377</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="C48" s="1">
         <v>2550</v>
@@ -15393,7 +15406,7 @@
         <v>378</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="C49" s="1">
         <v>2750</v>
@@ -15409,7 +15422,7 @@
         <v>379</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C50" s="1">
         <v>3200</v>
@@ -15425,7 +15438,7 @@
         <v>380</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="C51" s="1">
         <v>1050</v>
@@ -15441,7 +15454,7 @@
         <v>381</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="C52" s="1">
         <v>1050</v>
@@ -15457,7 +15470,7 @@
         <v>382</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="C53" s="1">
         <v>1200</v>
@@ -15473,7 +15486,7 @@
         <v>383</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="C54" s="1">
         <v>1050</v>
@@ -15489,7 +15502,7 @@
         <v>384</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="C55" s="1">
         <v>1550</v>
@@ -15505,7 +15518,7 @@
         <v>385</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="C56" s="1">
         <v>1200</v>
@@ -15521,7 +15534,7 @@
         <v>386</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="C57" s="1">
         <v>2100</v>
@@ -15537,7 +15550,7 @@
         <v>387</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="C58" s="1">
         <v>1100</v>
@@ -15553,7 +15566,7 @@
         <v>388</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="C59" s="1">
         <v>2500</v>
@@ -15569,7 +15582,7 @@
         <v>389</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="C60" s="1">
         <v>1400</v>
@@ -15585,7 +15598,7 @@
         <v>390</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="C61" s="1">
         <v>1800</v>
@@ -15601,7 +15614,7 @@
         <v>391</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="C62" s="1">
         <v>500</v>
@@ -15617,7 +15630,7 @@
         <v>392</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="C63" s="1">
         <v>600</v>
@@ -15633,7 +15646,7 @@
         <v>393</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="C64" s="1">
         <v>1250</v>
@@ -15649,7 +15662,7 @@
         <v>394</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="C65" s="1">
         <v>1350</v>
@@ -15665,7 +15678,7 @@
         <v>395</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="C66" s="1">
         <v>300</v>
@@ -15681,7 +15694,7 @@
         <v>396</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="C67" s="1">
         <v>1600</v>
@@ -15697,7 +15710,7 @@
         <v>397</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="C68" s="1">
         <v>550</v>
@@ -15713,7 +15726,7 @@
         <v>398</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="C69" s="1">
         <v>1750</v>
@@ -15729,7 +15742,7 @@
         <v>399</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="C70" s="1">
         <v>1050</v>
@@ -15745,7 +15758,7 @@
         <v>400</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="C71" s="1">
         <v>1750</v>
@@ -15761,7 +15774,7 @@
         <v>401</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="C72" s="1">
         <v>1050</v>
@@ -15777,7 +15790,7 @@
         <v>402</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="C73" s="1">
         <v>1750</v>
@@ -15793,7 +15806,7 @@
         <v>403</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="C74" s="1">
         <v>2100</v>
@@ -15809,7 +15822,7 @@
         <v>404</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="C75" s="1">
         <v>200</v>
@@ -15825,7 +15838,7 @@
         <v>405</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="C76" s="1">
         <v>600</v>
@@ -15841,7 +15854,7 @@
         <v>406</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="C77" s="1">
         <v>600</v>
@@ -15857,7 +15870,7 @@
         <v>407</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="C78" s="1">
         <v>2450</v>
@@ -15873,7 +15886,7 @@
         <v>408</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="C79" s="1">
         <v>2100</v>
@@ -15889,7 +15902,7 @@
         <v>409</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="C80" s="1">
         <v>2450</v>
@@ -15905,7 +15918,7 @@
         <v>410</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="C81" s="1">
         <v>1750</v>
@@ -15921,7 +15934,7 @@
         <v>411</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="C82" s="1">
         <v>2800</v>
@@ -15937,7 +15950,7 @@
         <v>412</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="C83" s="1">
         <v>1750</v>
@@ -15953,7 +15966,7 @@
         <v>413</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="C84" s="1">
         <v>1750</v>
@@ -15969,7 +15982,7 @@
         <v>414</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="C85" s="1">
         <v>2100</v>
@@ -15985,7 +15998,7 @@
         <v>415</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="C86" s="1">
         <v>1050</v>
@@ -16001,7 +16014,7 @@
         <v>416</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="C87" s="1">
         <v>50</v>
@@ -16017,7 +16030,7 @@
         <v>417</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="C88" s="1">
         <v>130</v>
@@ -16033,7 +16046,7 @@
         <v>418</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="C89" s="1">
         <v>280</v>
@@ -16048,7 +16061,7 @@
         <v>419</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="C90" s="1">
         <v>280</v>
@@ -16064,7 +16077,7 @@
         <v>420</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="C91" s="1">
         <v>1750</v>
@@ -16080,7 +16093,7 @@
         <v>421</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="C92" s="1">
         <v>1750</v>
@@ -16096,7 +16109,7 @@
         <v>422</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="C93" s="1">
         <v>1400</v>
@@ -16112,7 +16125,7 @@
         <v>423</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="C94" s="1">
         <v>600</v>
@@ -16128,7 +16141,7 @@
         <v>424</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="C95" s="1">
         <v>3550</v>
@@ -16144,7 +16157,7 @@
         <v>425</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="C96" s="1">
         <v>2800</v>
@@ -16160,7 +16173,7 @@
         <v>426</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="C97" s="1">
         <v>700</v>
@@ -16176,7 +16189,7 @@
         <v>427</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="C98" s="1">
         <v>200</v>
@@ -16192,7 +16205,7 @@
         <v>428</v>
       </c>
       <c r="B99" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="C99">
         <v>1100</v>
@@ -16208,7 +16221,7 @@
         <v>429</v>
       </c>
       <c r="B100" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="C100">
         <v>1750</v>
@@ -16224,7 +16237,7 @@
         <v>430</v>
       </c>
       <c r="B101" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="C101">
         <v>2700</v>
